--- a/docs/test-documentation/Test_Data_updated.xlsx
+++ b/docs/test-documentation/Test_Data_updated.xlsx
@@ -2,7 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Данные" sheetId="1" r:id="R4091cb2395b5491e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Данные" sheetId="1" r:id="R7a82f88ab1744d06"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DataProvider" sheetId="2" r:id="R077e7c2af3514f89"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Первоначальный план" sheetId="3" r:id="Rfa3734df05814041"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -45,7 +47,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="13">
+  <x:cellXfs count="14">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -73,6 +75,9 @@
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -81,13 +86,49 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TableTestData" displayName="TableTestData" ref="A1:E21" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:tableColumns count="5">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TableTestData" displayName="TableTestData" ref="A1:H44" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="8">
     <x:tableColumn id="1" name="ID"/>
     <x:tableColumn id="2" name="Категория"/>
     <x:tableColumn id="3" name="Назначение"/>
     <x:tableColumn id="4" name="Пример"/>
     <x:tableColumn id="5" name="Правила подготовки / безопасности"/>
+    <x:tableColumn id="6" name="Источник / DataProvider"/>
+    <x:tableColumn id="7" name="Актуальные кейсы"/>
+    <x:tableColumn id="8" name="Вариантов"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="DocData1" displayName="DocData1" ref="A1:I85" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="9">
+    <x:tableColumn id="1" name="ID строки"/>
+    <x:tableColumn id="2" name="ID набора"/>
+    <x:tableColumn id="3" name="Java-класс / DataProvider"/>
+    <x:tableColumn id="4" name="Вариант"/>
+    <x:tableColumn id="5" name="Данные без секретов"/>
+    <x:tableColumn id="6" name="Ожидаемый результат"/>
+    <x:tableColumn id="7" name="Актуальный кейс"/>
+    <x:tableColumn id="8" name="Статус"/>
+    <x:tableColumn id="9" name="Подтверждение запуска"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="DocData2" displayName="DocData2" ref="A1:H3" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="8">
+    <x:tableColumn id="1" name="ID"/>
+    <x:tableColumn id="2" name="Категория"/>
+    <x:tableColumn id="3" name="Назначение"/>
+    <x:tableColumn id="4" name="Пример"/>
+    <x:tableColumn id="5" name="Правила подготовки / безопасности"/>
+    <x:tableColumn id="6" name="Источник / DataProvider"/>
+    <x:tableColumn id="7" name="Актуальные кейсы"/>
+    <x:tableColumn id="8" name="Вариантов"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -288,31 +329,43 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="22" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="21" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="31" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="66" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="70" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="43" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="70" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="80" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="58" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="64" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="15" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="35" customHeight="1">
-      <x:c r="A1" s="5" t="str">
+    <x:row r="1" ht="38" customHeight="1">
+      <x:c r="A1" s="13" t="str">
         <x:v>ID</x:v>
       </x:c>
-      <x:c r="B1" s="5" t="str">
+      <x:c r="B1" s="13" t="str">
         <x:v>Категория</x:v>
       </x:c>
-      <x:c r="C1" s="5" t="str">
+      <x:c r="C1" s="13" t="str">
         <x:v>Назначение</x:v>
       </x:c>
-      <x:c r="D1" s="5" t="str">
+      <x:c r="D1" s="13" t="str">
         <x:v>Пример</x:v>
       </x:c>
-      <x:c r="E1" s="5" t="str">
+      <x:c r="E1" s="13" t="str">
         <x:v>Правила подготовки / безопасности</x:v>
       </x:c>
-    </x:row>
-    <x:row r="2" ht="46" customHeight="1">
+      <x:c r="F1" s="13" t="str">
+        <x:v>Источник / DataProvider</x:v>
+      </x:c>
+      <x:c r="G1" s="13" t="str">
+        <x:v>Актуальные кейсы</x:v>
+      </x:c>
+      <x:c r="H1" s="13" t="str">
+        <x:v>Вариантов</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="78" customHeight="1">
       <x:c r="A2" s="12" t="str">
         <x:v>TD-USER-NEW</x:v>
       </x:c>
@@ -323,13 +376,20 @@
         <x:v>Уникальный временный пользователь</x:v>
       </x:c>
       <x:c r="D2" s="12" t="str">
-        <x:v>qa_user_&lt;uuid&gt; / qa_&lt;uuid&gt;@example.test</x:v>
+        <x:v>qa_user_&lt;20 hex&gt;; qa_&lt;32 hex&gt;@example.test</x:v>
       </x:c>
       <x:c r="E2" s="12" t="str">
-        <x:v>Уникальный username/email на каждый прогон; пароль TEST_USER_PASSWORD из env; после теста вход и DELETE /api/users/me с CSRF; cleanup best effort</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" ht="46" customHeight="1">
+        <x:v>TestDataGenerator: уникальные значения; пароль из TEST_USER_PASSWORD, без публикации. JDBC teardown удаляет только зарегистрированные тестом данные.</x:v>
+      </x:c>
+      <x:c r="F2" s="12" t="str">
+        <x:v>Java TestData / TestDataGenerator / тестовый метод</x:v>
+      </x:c>
+      <x:c r="G2" s="12" t="str">
+        <x:v>API-001, API-002, API-003, API-004, API-021, API-026, API-027, API-028, API-041, API-042, API-043, UI-001, UI-002, UI-021, UI-032, UI-040</x:v>
+      </x:c>
+      <x:c r="H2" s="12"/>
+    </x:row>
+    <x:row r="3" ht="78" customHeight="1">
       <x:c r="A3" s="12" t="str">
         <x:v>TD-USER-EXIST</x:v>
       </x:c>
@@ -340,13 +400,20 @@
         <x:v>Занятый логин при повторной регистрации</x:v>
       </x:c>
       <x:c r="D3" s="12" t="str">
-        <x:v>qa_existing_&lt;uuid&gt;</x:v>
+        <x:v>API: первый временный пользователь; UI: TestData.EXISTING_USERNAME / EXISTING_EMAIL</x:v>
       </x:c>
       <x:c r="E3" s="12" t="str">
-        <x:v>Создать временный аккаунт до теста; повторить username с другим email; после теста удалить подготовленный аккаунт</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" ht="46" customHeight="1">
+        <x:v>Не публиковать секреты; не удалять постоянного пользователя. Дубликаты API готовятся внутри метода.</x:v>
+      </x:c>
+      <x:c r="F3" s="12" t="str">
+        <x:v>Java TestData / TestDataGenerator / тестовый метод</x:v>
+      </x:c>
+      <x:c r="G3" s="12" t="str">
+        <x:v>API-002, API-021, UI-002, UI-021, UI-040</x:v>
+      </x:c>
+      <x:c r="H3" s="12"/>
+    </x:row>
+    <x:row r="4" ht="78" customHeight="1">
       <x:c r="A4" s="12" t="str">
         <x:v>TD-USER-A</x:v>
       </x:c>
@@ -357,13 +424,20 @@
         <x:v>Постоянный тестовый пользователь для CRUD</x:v>
       </x:c>
       <x:c r="D4" s="12" t="str">
-        <x:v>autotest_user (отдельная тестовая среда)</x:v>
+        <x:v>TestData.EXISTING_USERNAME (значение не дублируется)</x:v>
       </x:c>
       <x:c r="E4" s="12" t="str">
-        <x:v>Завести заранее; пароль из env; не удалять аккаунт; задачи каждого теста очищать; не использовать общий изменяемый набор задач параллельно</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="46" customHeight="1">
+        <x:v>Постоянный тестовый пользователь; пароль из DPAPI/env. Задачи создаются и отслеживаются существующим cleanup.</x:v>
+      </x:c>
+      <x:c r="F4" s="12" t="str">
+        <x:v>Java TestData / TestDataGenerator / тестовый метод</x:v>
+      </x:c>
+      <x:c r="G4" s="12" t="str">
+        <x:v>API-006, API-008, API-009, API-011, API-012, API-013, API-015, API-022, API-023, API-025, API-029, API-030, API-031, API-037, API-038, API-039, API-040, API-044, UI-005, UI-006, UI-007, UI-011, UI-012, UI-013, UI-014, UI-016, UI-018, UI-025, UI-033, UI-034, UI-035, UI-036, UI-037, UI-038, UI-039</x:v>
+      </x:c>
+      <x:c r="H4" s="12"/>
+    </x:row>
+    <x:row r="5" ht="78" customHeight="1">
       <x:c r="A5" s="12" t="str">
         <x:v>TD-USERS-AB</x:v>
       </x:c>
@@ -374,13 +448,20 @@
         <x:v>Два независимых пользователя</x:v>
       </x:c>
       <x:c r="D5" s="12" t="str">
-        <x:v>autotest_user + qa_b_&lt;uuid&gt;</x:v>
+        <x:v>Постоянный владелец A и временный B; два SessionFilter</x:v>
       </x:c>
       <x:c r="E5" s="12" t="str">
-        <x:v>A — тестовый аккаунт; B — временный или отдельный аккаунт; отдельные cookies/CSRF; очистить задачу A и временного B</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="46" customHeight="1">
+        <x:v>TaskApiTest.shouldNotGetAnotherUsersTask: отдельные cookies/CSRF; GET/PUT/DELETE чужого ID — 404; очистка JDBC.</x:v>
+      </x:c>
+      <x:c r="F5" s="12" t="str">
+        <x:v>Java TestData / TestDataGenerator / тестовый метод</x:v>
+      </x:c>
+      <x:c r="G5" s="12" t="str">
+        <x:v>API-017</x:v>
+      </x:c>
+      <x:c r="H5" s="12"/>
+    </x:row>
+    <x:row r="6" ht="78" customHeight="1">
       <x:c r="A6" s="12" t="str">
         <x:v>TD-USER-UNKNOWN</x:v>
       </x:c>
@@ -391,13 +472,20 @@
         <x:v>Неизвестный логин</x:v>
       </x:c>
       <x:c r="D6" s="12" t="str">
-        <x:v>not_registered_&lt;uuid&gt;</x:v>
+        <x:v>TestData.NON_EXISTING_USERNAME</x:v>
       </x:c>
       <x:c r="E6" s="12" t="str">
-        <x:v>Не должен существовать в БД</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="46" customHeight="1">
+        <x:v>Используется в LoginTest и LoginUiTest; для входа не создаётся.</x:v>
+      </x:c>
+      <x:c r="F6" s="12" t="str">
+        <x:v>Java TestData / TestDataGenerator / тестовый метод</x:v>
+      </x:c>
+      <x:c r="G6" s="12" t="str">
+        <x:v>API-024, UI-006, UI-007</x:v>
+      </x:c>
+      <x:c r="H6" s="12"/>
+    </x:row>
+    <x:row r="7" ht="78" customHeight="1">
       <x:c r="A7" s="12" t="str">
         <x:v>TD-EMAIL-BAD</x:v>
       </x:c>
@@ -411,10 +499,17 @@
         <x:v>invalid-email</x:v>
       </x:c>
       <x:c r="E7" s="12" t="str">
-        <x:v>Уникальный username, пароль из env; отсутствие регистрации; HTTP 400 уточнить по валидации DTO</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="46" customHeight="1">
+        <x:v>API invalidEmails: 3 варианта; UI invalidEmails: 4. Все строки перечислены на листе DataProvider.</x:v>
+      </x:c>
+      <x:c r="F7" s="12" t="str">
+        <x:v>Java TestData / TestDataGenerator / тестовый метод</x:v>
+      </x:c>
+      <x:c r="G7" s="12" t="str">
+        <x:v>API-003, UI-003</x:v>
+      </x:c>
+      <x:c r="H7" s="12"/>
+    </x:row>
+    <x:row r="8" ht="78" customHeight="1">
       <x:c r="A8" s="12" t="str">
         <x:v>TD-EMPTY</x:v>
       </x:c>
@@ -428,10 +523,17 @@
         <x:v>username=""; email=""; password=""</x:v>
       </x:c>
       <x:c r="E8" s="12" t="str">
-        <x:v>Проверить аннотации в RegisterRequestDto; без сохранения пользователя</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="46" customHeight="1">
+        <x:v>Пустые поля и приоритет проверяемого поля перечислены в DataProvider; не утверждать проверку всех полей при одном вызове.</x:v>
+      </x:c>
+      <x:c r="F8" s="12" t="str">
+        <x:v>Java TestData / TestDataGenerator / тестовый метод</x:v>
+      </x:c>
+      <x:c r="G8" s="12" t="str">
+        <x:v>API-004, UI-004, UI-025</x:v>
+      </x:c>
+      <x:c r="H8" s="12"/>
+    </x:row>
+    <x:row r="9" ht="78" customHeight="1">
       <x:c r="A9" s="12" t="str">
         <x:v>TD-PASSWORD-BAD</x:v>
       </x:c>
@@ -442,13 +544,20 @@
         <x:v>Неверный пароль</x:v>
       </x:c>
       <x:c r="D9" s="12" t="str">
-        <x:v>wrong-password</x:v>
+        <x:v>TestData.INVALID_PASSWORD (значение не публикуется)</x:v>
       </x:c>
       <x:c r="E9" s="12" t="str">
-        <x:v>Не сохранять настоящие пароли в Git</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="46" customHeight="1">
+        <x:v>Заведомо неверный пароль; никакие реальные пароли в документах не сохраняются.</x:v>
+      </x:c>
+      <x:c r="F9" s="12" t="str">
+        <x:v>Java TestData / TestDataGenerator / тестовый метод</x:v>
+      </x:c>
+      <x:c r="G9" s="12" t="str">
+        <x:v>API-023, API-024, UI-006, UI-007</x:v>
+      </x:c>
+      <x:c r="H9" s="12"/>
+    </x:row>
+    <x:row r="10" ht="78" customHeight="1">
       <x:c r="A10" s="12" t="str">
         <x:v>TD-NO-SESSION</x:v>
       </x:c>
@@ -464,198 +573,3464 @@
       <x:c r="E10" s="12" t="str">
         <x:v>Чистый HTTP-клиент / браузер</x:v>
       </x:c>
-    </x:row>
-    <x:row r="11" ht="46" customHeight="1">
+      <x:c r="F10" s="12" t="str">
+        <x:v>Java TestData / TestDataGenerator / тестовый метод</x:v>
+      </x:c>
+      <x:c r="G10" s="12" t="str">
+        <x:v>API-020, API-036, UI-023, UI-024, UI-026, UI-027, UI-028, UI-029, UI-030</x:v>
+      </x:c>
+      <x:c r="H10" s="12"/>
+    </x:row>
+    <x:row r="11" ht="78" customHeight="1">
       <x:c r="A11" s="12" t="str">
-        <x:v>TD-NO-CSRF</x:v>
+        <x:v>TD-TASK-MIN</x:v>
       </x:c>
       <x:c r="B11" s="12" t="str">
-        <x:v>CSRF</x:v>
+        <x:v>Задача</x:v>
       </x:c>
       <x:c r="C11" s="12" t="str">
-        <x:v>Запрос изменения данных без CSRF</x:v>
+        <x:v>Минимальный набор</x:v>
       </x:c>
       <x:c r="D11" s="12" t="str">
-        <x:v>X-CSRF-TOKEN отсутствует</x:v>
+        <x:v>AUTOTEST_&lt;uuid&gt;; описание из метода</x:v>
       </x:c>
       <x:c r="E11" s="12" t="str">
-        <x:v>Использовать авторизованную сессию; намеренно не отправлять токен; проверить HTTP 403 и отсутствие изменений</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" ht="46" customHeight="1">
+        <x:v>API generator: TODO/MEDIUM/2026-12-31. UI минимальный сценарий: TODO/LOW/deadline=NULL.</x:v>
+      </x:c>
+      <x:c r="F11" s="12" t="str">
+        <x:v>Java TestData / TestDataGenerator / тестовый метод</x:v>
+      </x:c>
+      <x:c r="G11" s="12" t="str">
+        <x:v>API-008, UI-011</x:v>
+      </x:c>
+      <x:c r="H11" s="12"/>
+    </x:row>
+    <x:row r="12" ht="78" customHeight="1">
       <x:c r="A12" s="12" t="str">
-        <x:v>TD-TASK-MIN</x:v>
+        <x:v>TD-TASK-FULL</x:v>
       </x:c>
       <x:c r="B12" s="12" t="str">
         <x:v>Задача</x:v>
       </x:c>
       <x:c r="C12" s="12" t="str">
-        <x:v>Минимальный набор</x:v>
+        <x:v>Полный набор полей задачи</x:v>
       </x:c>
       <x:c r="D12" s="12" t="str">
-        <x:v>title=Task_&lt;uuid&gt;</x:v>
+        <x:v>AUTOTEST_&lt;uuid&gt;; status/priority/deadline из метода или provider</x:v>
       </x:c>
       <x:c r="E12" s="12" t="str">
-        <x:v>Остальные поля — по контракту</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" ht="46" customHeight="1">
+        <x:v>UI all fields: IN_PROGRESS/HIGH/2026-12-31; UI taskData — три конкретных сочетания; API default — TODO/MEDIUM/2026-12-31.</x:v>
+      </x:c>
+      <x:c r="F12" s="12" t="str">
+        <x:v>Java TestData / TestDataGenerator / тестовый метод</x:v>
+      </x:c>
+      <x:c r="G12" s="12" t="str">
+        <x:v>API-006, API-011, API-017, UI-012, UI-035, UI-038</x:v>
+      </x:c>
+      <x:c r="H12" s="12"/>
+    </x:row>
+    <x:row r="13" ht="78" customHeight="1">
       <x:c r="A13" s="12" t="str">
-        <x:v>TD-TASK-FULL</x:v>
+        <x:v>TD-TASK-UPDATE</x:v>
       </x:c>
       <x:c r="B13" s="12" t="str">
         <x:v>Задача</x:v>
       </x:c>
       <x:c r="C13" s="12" t="str">
-        <x:v>Полный набор полей задачи</x:v>
+        <x:v>Обновление</x:v>
       </x:c>
       <x:c r="D13" s="12" t="str">
-        <x:v>title=VKR_&lt;uuid&gt;; description=Automation; status=TODO; priority=HIGH; deadline=2027-02-15</x:v>
+        <x:v>Новое описание; IN_PROGRESS/HIGH</x:v>
       </x:c>
       <x:c r="E13" s="12" t="str">
-        <x:v>Уникальное название; значения и допустимость срока сверить с DTO; сохранить ID для очистки</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" ht="46" customHeight="1">
+        <x:v>API и UI сохраняют название и дедлайн; проверяют описание, статус и приоритет. Утверждения об изменении title/deadline не добавлены.</x:v>
+      </x:c>
+      <x:c r="F13" s="12" t="str">
+        <x:v>Java TestData / TestDataGenerator / тестовый метод</x:v>
+      </x:c>
+      <x:c r="G13" s="12" t="str">
+        <x:v>API-013, API-040, UI-016</x:v>
+      </x:c>
+      <x:c r="H13" s="12"/>
+    </x:row>
+    <x:row r="14" ht="78" customHeight="1">
       <x:c r="A14" s="12" t="str">
-        <x:v>TD-TASK-UPDATE</x:v>
+        <x:v>TD-TITLE-EMPTY</x:v>
       </x:c>
       <x:c r="B14" s="12" t="str">
         <x:v>Задача</x:v>
       </x:c>
       <x:c r="C14" s="12" t="str">
-        <x:v>Обновление</x:v>
+        <x:v>Название задачи отсутствует</x:v>
       </x:c>
       <x:c r="D14" s="12" t="str">
-        <x:v>title=Updated_&lt;uuid&gt;</x:v>
+        <x:v>title=""</x:v>
       </x:c>
       <x:c r="E14" s="12" t="str">
-        <x:v>Создать новую задачу перед тестом</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" ht="46" customHeight="1">
+        <x:v>API POST: 400; UI: сообщения обязательности и длины 3–100, URL /tasks/new.</x:v>
+      </x:c>
+      <x:c r="F14" s="12" t="str">
+        <x:v>Java TestData / TestDataGenerator / тестовый метод</x:v>
+      </x:c>
+      <x:c r="G14" s="12" t="str">
+        <x:v>API-009, API-029, API-044, UI-013</x:v>
+      </x:c>
+      <x:c r="H14" s="12"/>
+    </x:row>
+    <x:row r="15" ht="78" customHeight="1">
       <x:c r="A15" s="12" t="str">
-        <x:v>TD-TITLE-EMPTY</x:v>
+        <x:v>TD-TITLE-LONG</x:v>
       </x:c>
       <x:c r="B15" s="12" t="str">
         <x:v>Задача</x:v>
       </x:c>
       <x:c r="C15" s="12" t="str">
-        <x:v>Название задачи отсутствует</x:v>
+        <x:v>Длинное название</x:v>
       </x:c>
       <x:c r="D15" s="12" t="str">
-        <x:v>title=""</x:v>
+        <x:v>Ввод названия длиной 101</x:v>
       </x:c>
       <x:c r="E15" s="12" t="str">
-        <x:v>Проверить DTO-валидацию; тест не должен оставлять некорректную задачу</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" ht="46" customHeight="1">
+        <x:v>API: 400. UI: поле ограничено первыми 100 символами; отправка в этом UI-кейсе не выполняется.</x:v>
+      </x:c>
+      <x:c r="F15" s="12" t="str">
+        <x:v>Java TestData / TestDataGenerator / тестовый метод</x:v>
+      </x:c>
+      <x:c r="G15" s="12" t="str">
+        <x:v>API-009, API-029, API-044, UI-014</x:v>
+      </x:c>
+      <x:c r="H15" s="12"/>
+    </x:row>
+    <x:row r="16" ht="78" customHeight="1">
       <x:c r="A16" s="12" t="str">
-        <x:v>TD-TITLE-LONG</x:v>
+        <x:v>TD-STATUS</x:v>
       </x:c>
       <x:c r="B16" s="12" t="str">
+        <x:v>Статус</x:v>
+      </x:c>
+      <x:c r="C16" s="12" t="str">
+        <x:v>Смена статуса</x:v>
+      </x:c>
+      <x:c r="D16" s="12" t="str">
+        <x:v>TODO, IN_PROGRESS, DONE</x:v>
+      </x:c>
+      <x:c r="E16" s="12" t="str">
+        <x:v>API validTaskStatuses и сочетания UI taskData; строки различаются по контексту.</x:v>
+      </x:c>
+      <x:c r="F16" s="12" t="str">
+        <x:v>Java TestData / TestDataGenerator / тестовый метод</x:v>
+      </x:c>
+      <x:c r="G16" s="12" t="str">
+        <x:v>API-038</x:v>
+      </x:c>
+      <x:c r="H16" s="12"/>
+    </x:row>
+    <x:row r="17" ht="78" customHeight="1">
+      <x:c r="A17" s="12" t="str">
+        <x:v>TD-PRIORITY</x:v>
+      </x:c>
+      <x:c r="B17" s="12" t="str">
+        <x:v>Приоритет</x:v>
+      </x:c>
+      <x:c r="C17" s="12" t="str">
+        <x:v>Приоритет и срок</x:v>
+      </x:c>
+      <x:c r="D17" s="12" t="str">
+        <x:v>LOW, MEDIUM, HIGH</x:v>
+      </x:c>
+      <x:c r="E17" s="12" t="str">
+        <x:v>API validTaskPriorities и сочетания UI taskData. Дедлайны заданы конкретными методами, не берутся из первоначального плана.</x:v>
+      </x:c>
+      <x:c r="F17" s="12" t="str">
+        <x:v>Java TestData / TestDataGenerator / тестовый метод</x:v>
+      </x:c>
+      <x:c r="G17" s="12" t="str">
+        <x:v>API-039</x:v>
+      </x:c>
+      <x:c r="H17" s="12"/>
+    </x:row>
+    <x:row r="18" ht="78" customHeight="1">
+      <x:c r="A18" s="12" t="str">
+        <x:v>TD-TASK-DELETE</x:v>
+      </x:c>
+      <x:c r="B18" s="12" t="str">
         <x:v>Задача</x:v>
       </x:c>
-      <x:c r="C16" s="12" t="str">
-        <x:v>Длинное название</x:v>
-      </x:c>
-      <x:c r="D16" s="12" t="str">
-        <x:v>title=А × 256</x:v>
-      </x:c>
-      <x:c r="E16" s="12" t="str">
-        <x:v>Предел длины уточнить по DTO/БД</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" ht="46" customHeight="1">
-      <x:c r="A17" s="12" t="str">
-        <x:v>TD-STATUS</x:v>
-      </x:c>
-      <x:c r="B17" s="12" t="str">
-        <x:v>Статус</x:v>
-      </x:c>
-      <x:c r="C17" s="12" t="str">
-        <x:v>Смена статуса</x:v>
-      </x:c>
-      <x:c r="D17" s="12" t="str">
-        <x:v>TODO → IN_PROGRESS</x:v>
-      </x:c>
-      <x:c r="E17" s="12" t="str">
-        <x:v>Допустимые значения enum</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="46" customHeight="1">
-      <x:c r="A18" s="12" t="str">
-        <x:v>TD-PRIORITY</x:v>
-      </x:c>
-      <x:c r="B18" s="12" t="str">
-        <x:v>Приоритет</x:v>
-      </x:c>
       <x:c r="C18" s="12" t="str">
-        <x:v>Приоритет и срок</x:v>
+        <x:v>Собственная задача для удаления</x:v>
       </x:c>
       <x:c r="D18" s="12" t="str">
-        <x:v>LOW → HIGH; deadline=2027-02-15</x:v>
+        <x:v>Собственная AUTOTEST_&lt;uuid&gt; задача</x:v>
       </x:c>
       <x:c r="E18" s="12" t="str">
-        <x:v>Дата должна быть допустима</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="46" customHeight="1">
+        <x:v>Создать в начале метода. Подтвердить удаление либо отменить; существующий teardown очищает оставшиеся собственные данные.</x:v>
+      </x:c>
+      <x:c r="F18" s="12" t="str">
+        <x:v>Java TestData / TestDataGenerator / тестовый метод</x:v>
+      </x:c>
+      <x:c r="G18" s="12" t="str">
+        <x:v>API-015, UI-018, UI-039</x:v>
+      </x:c>
+      <x:c r="H18" s="12"/>
+    </x:row>
+    <x:row r="19" ht="78" customHeight="1">
       <x:c r="A19" s="12" t="str">
-        <x:v>TD-TASK-DELETE</x:v>
+        <x:v>TD-ID-MISSING</x:v>
       </x:c>
       <x:c r="B19" s="12" t="str">
-        <x:v>Задача</x:v>
+        <x:v>ID</x:v>
       </x:c>
       <x:c r="C19" s="12" t="str">
-        <x:v>Собственная задача для удаления</x:v>
+        <x:v>Несуществующий идентификатор</x:v>
       </x:c>
       <x:c r="D19" s="12" t="str">
-        <x:v>title=Delete_&lt;uuid&gt;</x:v>
+        <x:v>-1</x:v>
       </x:c>
       <x:c r="E19" s="12" t="str">
-        <x:v>Создать непосредственно перед тестом; сохранить ID; в teardown удалять только если осталась</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" ht="46" customHeight="1">
+        <x:v>TaskApiTest.shouldNotGetNonExistingTask: HTTP 404. Удалённый ID — отдельная связанная проверка API-016.</x:v>
+      </x:c>
+      <x:c r="F19" s="12" t="str">
+        <x:v>Java TestData / TestDataGenerator / тестовый метод</x:v>
+      </x:c>
+      <x:c r="G19" s="12" t="str">
+        <x:v>API-012</x:v>
+      </x:c>
+      <x:c r="H19" s="12"/>
+    </x:row>
+    <x:row r="20" ht="78" customHeight="1">
       <x:c r="A20" s="12" t="str">
-        <x:v>TD-ID-MISSING</x:v>
+        <x:v>TD-DB-TEST</x:v>
       </x:c>
       <x:c r="B20" s="12" t="str">
-        <x:v>ID</x:v>
+        <x:v>Инфраструктура</x:v>
       </x:c>
       <x:c r="C20" s="12" t="str">
-        <x:v>Несуществующий идентификатор</x:v>
+        <x:v>Выделенная тестовая PostgreSQL</x:v>
       </x:c>
       <x:c r="D20" s="12" t="str">
-        <x:v>ID, отсутствующий в БД</x:v>
+        <x:v>TEST_DB_URL / USERNAME / PASSWORD, разрешённые hostname и порт — без значений</x:v>
       </x:c>
       <x:c r="E20" s="12" t="str">
-        <x:v>Не полагаться на фиксированное число</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" ht="46" customHeight="1">
+        <x:v>DbConnectionTest проверяет current_database()=task_manager_test; никаких SQL-запросов к production.</x:v>
+      </x:c>
+      <x:c r="F20" s="12" t="str">
+        <x:v>Java TestData / TestDataGenerator / тестовый метод</x:v>
+      </x:c>
+      <x:c r="G20" s="12" t="str">
+        <x:v>API-035</x:v>
+      </x:c>
+      <x:c r="H20" s="12"/>
+    </x:row>
+    <x:row r="21" ht="78" customHeight="1">
       <x:c r="A21" s="12" t="str">
-        <x:v>TD-HTML-TEXT</x:v>
+        <x:v>TD-EMAIL-VALID</x:v>
       </x:c>
       <x:c r="B21" s="12" t="str">
-        <x:v>Текст</x:v>
+        <x:v>Email</x:v>
       </x:c>
       <x:c r="C21" s="12" t="str">
-        <x:v>HTML-подобное значение</x:v>
+        <x:v>Корректный формат email</x:v>
       </x:c>
       <x:c r="D21" s="12" t="str">
-        <x:v>&lt;script&gt;alert(1)&lt;/script&gt;</x:v>
+        <x:v>TestData.VALID_EMAIL</x:v>
       </x:c>
       <x:c r="E21" s="12" t="str">
-        <x:v>Проверять отображение как текста, без выполнения</x:v>
+        <x:v>RegistrationUiTest.shouldAcceptValidEmail проверяет typeMismatch=false; регистрация не отправляется.</x:v>
+      </x:c>
+      <x:c r="F21" s="12" t="str">
+        <x:v>Java TestData / TestDataGenerator / тестовый метод</x:v>
+      </x:c>
+      <x:c r="G21" s="12" t="str">
+        <x:v>UI-031</x:v>
+      </x:c>
+      <x:c r="H21" s="12"/>
+    </x:row>
+    <x:row r="22" ht="78" customHeight="1">
+      <x:c r="A22" s="12" t="str">
+        <x:v>DP-A-REG-EMAIL</x:v>
+      </x:c>
+      <x:c r="B22" s="12" t="str">
+        <x:v>DataProvider</x:v>
+      </x:c>
+      <x:c r="C22" s="12" t="str">
+        <x:v>Варианты RegistrationTest.invalidEmails</x:v>
+      </x:c>
+      <x:c r="D22" s="12" t="str">
+        <x:v>См. лист DataProvider: строки 1–3</x:v>
+      </x:c>
+      <x:c r="E22" s="12" t="str">
+        <x:v>Базовые данные: TD-USER-NEW, TD-EMAIL-BAD. Значения паролей заменены описанием назначения или длины.</x:v>
+      </x:c>
+      <x:c r="F22" s="12" t="str">
+        <x:v>RegistrationTest.invalidEmails</x:v>
+      </x:c>
+      <x:c r="G22" s="12" t="str">
+        <x:v>API-003</x:v>
+      </x:c>
+      <x:c r="H22" s="12" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="78" customHeight="1">
+      <x:c r="A23" s="12" t="str">
+        <x:v>DP-A-REG-EMPTY</x:v>
+      </x:c>
+      <x:c r="B23" s="12" t="str">
+        <x:v>DataProvider</x:v>
+      </x:c>
+      <x:c r="C23" s="12" t="str">
+        <x:v>Варианты RegistrationTest.emptyRequiredFields</x:v>
+      </x:c>
+      <x:c r="D23" s="12" t="str">
+        <x:v>См. лист DataProvider: строки 1–3</x:v>
+      </x:c>
+      <x:c r="E23" s="12" t="str">
+        <x:v>Базовые данные: TD-USER-NEW, TD-EMPTY. Значения паролей заменены описанием назначения или длины.</x:v>
+      </x:c>
+      <x:c r="F23" s="12" t="str">
+        <x:v>RegistrationTest.emptyRequiredFields</x:v>
+      </x:c>
+      <x:c r="G23" s="12" t="str">
+        <x:v>API-004</x:v>
+      </x:c>
+      <x:c r="H23" s="12" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="78" customHeight="1">
+      <x:c r="A24" s="12" t="str">
+        <x:v>DP-A-REG-USERLEN</x:v>
+      </x:c>
+      <x:c r="B24" s="12" t="str">
+        <x:v>DataProvider</x:v>
+      </x:c>
+      <x:c r="C24" s="12" t="str">
+        <x:v>Варианты RegistrationTest.usernameBoundaries</x:v>
+      </x:c>
+      <x:c r="D24" s="12" t="str">
+        <x:v>См. лист DataProvider: строки 1–4</x:v>
+      </x:c>
+      <x:c r="E24" s="12" t="str">
+        <x:v>Базовые данные: TD-USER-NEW. Значения паролей заменены описанием назначения или длины.</x:v>
+      </x:c>
+      <x:c r="F24" s="12" t="str">
+        <x:v>RegistrationTest.usernameBoundaries</x:v>
+      </x:c>
+      <x:c r="G24" s="12" t="str">
+        <x:v>API-026, API-028, API-041</x:v>
+      </x:c>
+      <x:c r="H24" s="12" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="78" customHeight="1">
+      <x:c r="A25" s="12" t="str">
+        <x:v>DP-A-REG-PASSLEN</x:v>
+      </x:c>
+      <x:c r="B25" s="12" t="str">
+        <x:v>DataProvider</x:v>
+      </x:c>
+      <x:c r="C25" s="12" t="str">
+        <x:v>Варианты RegistrationTest.passwordBoundaries</x:v>
+      </x:c>
+      <x:c r="D25" s="12" t="str">
+        <x:v>См. лист DataProvider: строки 1–4</x:v>
+      </x:c>
+      <x:c r="E25" s="12" t="str">
+        <x:v>Базовые данные: TD-USER-NEW. Значения паролей заменены описанием назначения или длины.</x:v>
+      </x:c>
+      <x:c r="F25" s="12" t="str">
+        <x:v>RegistrationTest.passwordBoundaries</x:v>
+      </x:c>
+      <x:c r="G25" s="12" t="str">
+        <x:v>API-027, API-042, API-043</x:v>
+      </x:c>
+      <x:c r="H25" s="12" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="78" customHeight="1">
+      <x:c r="A26" s="12" t="str">
+        <x:v>DP-A-TASK-BADTITLE</x:v>
+      </x:c>
+      <x:c r="B26" s="12" t="str">
+        <x:v>DataProvider</x:v>
+      </x:c>
+      <x:c r="C26" s="12" t="str">
+        <x:v>Варианты TaskApiTest.invalidTaskTitles</x:v>
+      </x:c>
+      <x:c r="D26" s="12" t="str">
+        <x:v>См. лист DataProvider: строки 1–3</x:v>
+      </x:c>
+      <x:c r="E26" s="12" t="str">
+        <x:v>Базовые данные: TD-USER-A, TD-TITLE-EMPTY, TD-TITLE-LONG. Значения паролей заменены описанием назначения или длины.</x:v>
+      </x:c>
+      <x:c r="F26" s="12" t="str">
+        <x:v>TaskApiTest.invalidTaskTitles</x:v>
+      </x:c>
+      <x:c r="G26" s="12" t="str">
+        <x:v>API-009, API-029, API-044</x:v>
+      </x:c>
+      <x:c r="H26" s="12" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="78" customHeight="1">
+      <x:c r="A27" s="12" t="str">
+        <x:v>DP-A-TASK-TITLELEN</x:v>
+      </x:c>
+      <x:c r="B27" s="12" t="str">
+        <x:v>DataProvider</x:v>
+      </x:c>
+      <x:c r="C27" s="12" t="str">
+        <x:v>Варианты TaskApiTest.validTaskTitleBoundaries</x:v>
+      </x:c>
+      <x:c r="D27" s="12" t="str">
+        <x:v>См. лист DataProvider: строки 1–2</x:v>
+      </x:c>
+      <x:c r="E27" s="12" t="str">
+        <x:v>Базовые данные: TD-USER-A. Значения паролей заменены описанием назначения или длины.</x:v>
+      </x:c>
+      <x:c r="F27" s="12" t="str">
+        <x:v>TaskApiTest.validTaskTitleBoundaries</x:v>
+      </x:c>
+      <x:c r="G27" s="12" t="str">
+        <x:v>API-037</x:v>
+      </x:c>
+      <x:c r="H27" s="12" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="78" customHeight="1">
+      <x:c r="A28" s="12" t="str">
+        <x:v>DP-A-TASK-STATUS</x:v>
+      </x:c>
+      <x:c r="B28" s="12" t="str">
+        <x:v>DataProvider</x:v>
+      </x:c>
+      <x:c r="C28" s="12" t="str">
+        <x:v>Варианты TaskApiTest.validTaskStatuses</x:v>
+      </x:c>
+      <x:c r="D28" s="12" t="str">
+        <x:v>См. лист DataProvider: строки 1–3</x:v>
+      </x:c>
+      <x:c r="E28" s="12" t="str">
+        <x:v>Базовые данные: TD-USER-A, TD-STATUS. Значения паролей заменены описанием назначения или длины.</x:v>
+      </x:c>
+      <x:c r="F28" s="12" t="str">
+        <x:v>TaskApiTest.validTaskStatuses</x:v>
+      </x:c>
+      <x:c r="G28" s="12" t="str">
+        <x:v>API-038</x:v>
+      </x:c>
+      <x:c r="H28" s="12" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="78" customHeight="1">
+      <x:c r="A29" s="12" t="str">
+        <x:v>DP-A-TASK-PRIORITY</x:v>
+      </x:c>
+      <x:c r="B29" s="12" t="str">
+        <x:v>DataProvider</x:v>
+      </x:c>
+      <x:c r="C29" s="12" t="str">
+        <x:v>Варианты TaskApiTest.validTaskPriorities</x:v>
+      </x:c>
+      <x:c r="D29" s="12" t="str">
+        <x:v>См. лист DataProvider: строки 1–3</x:v>
+      </x:c>
+      <x:c r="E29" s="12" t="str">
+        <x:v>Базовые данные: TD-USER-A, TD-PRIORITY. Значения паролей заменены описанием назначения или длины.</x:v>
+      </x:c>
+      <x:c r="F29" s="12" t="str">
+        <x:v>TaskApiTest.validTaskPriorities</x:v>
+      </x:c>
+      <x:c r="G29" s="12" t="str">
+        <x:v>API-039</x:v>
+      </x:c>
+      <x:c r="H29" s="12" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="78" customHeight="1">
+      <x:c r="A30" s="12" t="str">
+        <x:v>DP-A-TASK-BADENUM</x:v>
+      </x:c>
+      <x:c r="B30" s="12" t="str">
+        <x:v>DataProvider</x:v>
+      </x:c>
+      <x:c r="C30" s="12" t="str">
+        <x:v>Варианты TaskApiTest.invalidTaskEnums</x:v>
+      </x:c>
+      <x:c r="D30" s="12" t="str">
+        <x:v>См. лист DataProvider: строки 1–4</x:v>
+      </x:c>
+      <x:c r="E30" s="12" t="str">
+        <x:v>Базовые данные: TD-USER-A. Значения паролей заменены описанием назначения или длины.</x:v>
+      </x:c>
+      <x:c r="F30" s="12" t="str">
+        <x:v>TaskApiTest.invalidTaskEnums</x:v>
+      </x:c>
+      <x:c r="G30" s="12" t="str">
+        <x:v>API-030, API-031</x:v>
+      </x:c>
+      <x:c r="H30" s="12" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="78" customHeight="1">
+      <x:c r="A31" s="12" t="str">
+        <x:v>DP-A-TASK-BADUPDATE</x:v>
+      </x:c>
+      <x:c r="B31" s="12" t="str">
+        <x:v>DataProvider</x:v>
+      </x:c>
+      <x:c r="C31" s="12" t="str">
+        <x:v>Варианты TaskApiTest.invalidTaskUpdateData</x:v>
+      </x:c>
+      <x:c r="D31" s="12" t="str">
+        <x:v>См. лист DataProvider: строки 1–5</x:v>
+      </x:c>
+      <x:c r="E31" s="12" t="str">
+        <x:v>Базовые данные: TD-USER-A, TD-TASK-UPDATE. Значения паролей заменены описанием назначения или длины.</x:v>
+      </x:c>
+      <x:c r="F31" s="12" t="str">
+        <x:v>TaskApiTest.invalidTaskUpdateData</x:v>
+      </x:c>
+      <x:c r="G31" s="12" t="str">
+        <x:v>API-040</x:v>
+      </x:c>
+      <x:c r="H31" s="12" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="78" customHeight="1">
+      <x:c r="A32" s="12" t="str">
+        <x:v>DP-U-LOGIN-ELEMENT</x:v>
+      </x:c>
+      <x:c r="B32" s="12" t="str">
+        <x:v>DataProvider</x:v>
+      </x:c>
+      <x:c r="C32" s="12" t="str">
+        <x:v>Варианты LoginUiTest.loginElements</x:v>
+      </x:c>
+      <x:c r="D32" s="12" t="str">
+        <x:v>См. лист DataProvider: строки 1–5</x:v>
+      </x:c>
+      <x:c r="E32" s="12" t="str">
+        <x:v>Базовые данные: TD-NO-SESSION. Значения паролей заменены описанием назначения или длины.</x:v>
+      </x:c>
+      <x:c r="F32" s="12" t="str">
+        <x:v>LoginUiTest.loginElements</x:v>
+      </x:c>
+      <x:c r="G32" s="12" t="str">
+        <x:v>UI-024</x:v>
+      </x:c>
+      <x:c r="H32" s="12" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="78" customHeight="1">
+      <x:c r="A33" s="12" t="str">
+        <x:v>DP-U-LOGIN-BAD</x:v>
+      </x:c>
+      <x:c r="B33" s="12" t="str">
+        <x:v>DataProvider</x:v>
+      </x:c>
+      <x:c r="C33" s="12" t="str">
+        <x:v>Варианты LoginUiTest.invalidCredentials</x:v>
+      </x:c>
+      <x:c r="D33" s="12" t="str">
+        <x:v>См. лист DataProvider: строки 1–3</x:v>
+      </x:c>
+      <x:c r="E33" s="12" t="str">
+        <x:v>Базовые данные: TD-USER-A, TD-USER-UNKNOWN, TD-PASSWORD-BAD. Значения паролей заменены описанием назначения или длины.</x:v>
+      </x:c>
+      <x:c r="F33" s="12" t="str">
+        <x:v>LoginUiTest.invalidCredentials</x:v>
+      </x:c>
+      <x:c r="G33" s="12" t="str">
+        <x:v>UI-006, UI-007</x:v>
+      </x:c>
+      <x:c r="H33" s="12" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="78" customHeight="1">
+      <x:c r="A34" s="12" t="str">
+        <x:v>DP-U-LOGIN-EMPTY</x:v>
+      </x:c>
+      <x:c r="B34" s="12" t="str">
+        <x:v>DataProvider</x:v>
+      </x:c>
+      <x:c r="C34" s="12" t="str">
+        <x:v>Варианты LoginUiTest.emptyCredentials</x:v>
+      </x:c>
+      <x:c r="D34" s="12" t="str">
+        <x:v>См. лист DataProvider: строки 1–3</x:v>
+      </x:c>
+      <x:c r="E34" s="12" t="str">
+        <x:v>Базовые данные: TD-USER-A, TD-EMPTY. Значения паролей заменены описанием назначения или длины.</x:v>
+      </x:c>
+      <x:c r="F34" s="12" t="str">
+        <x:v>LoginUiTest.emptyCredentials</x:v>
+      </x:c>
+      <x:c r="G34" s="12" t="str">
+        <x:v>UI-025</x:v>
+      </x:c>
+      <x:c r="H34" s="12" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="78" customHeight="1">
+      <x:c r="A35" s="12" t="str">
+        <x:v>DP-U-REG-ELEMENT</x:v>
+      </x:c>
+      <x:c r="B35" s="12" t="str">
+        <x:v>DataProvider</x:v>
+      </x:c>
+      <x:c r="C35" s="12" t="str">
+        <x:v>Варианты RegistrationUiTest.registrationElements</x:v>
+      </x:c>
+      <x:c r="D35" s="12" t="str">
+        <x:v>См. лист DataProvider: строки 1–6</x:v>
+      </x:c>
+      <x:c r="E35" s="12" t="str">
+        <x:v>Базовые данные: TD-NO-SESSION. Значения паролей заменены описанием назначения или длины.</x:v>
+      </x:c>
+      <x:c r="F35" s="12" t="str">
+        <x:v>RegistrationUiTest.registrationElements</x:v>
+      </x:c>
+      <x:c r="G35" s="12" t="str">
+        <x:v>UI-027</x:v>
+      </x:c>
+      <x:c r="H35" s="12" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" ht="78" customHeight="1">
+      <x:c r="A36" s="12" t="str">
+        <x:v>DP-U-REG-EMPTY</x:v>
+      </x:c>
+      <x:c r="B36" s="12" t="str">
+        <x:v>DataProvider</x:v>
+      </x:c>
+      <x:c r="C36" s="12" t="str">
+        <x:v>Варианты RegistrationUiTest.emptyRegistrationFields</x:v>
+      </x:c>
+      <x:c r="D36" s="12" t="str">
+        <x:v>См. лист DataProvider: строки 1–4</x:v>
+      </x:c>
+      <x:c r="E36" s="12" t="str">
+        <x:v>Базовые данные: TD-EMPTY. Значения паролей заменены описанием назначения или длины.</x:v>
+      </x:c>
+      <x:c r="F36" s="12" t="str">
+        <x:v>RegistrationUiTest.emptyRegistrationFields</x:v>
+      </x:c>
+      <x:c r="G36" s="12" t="str">
+        <x:v>UI-004</x:v>
+      </x:c>
+      <x:c r="H36" s="12" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" ht="78" customHeight="1">
+      <x:c r="A37" s="12" t="str">
+        <x:v>DP-U-REG-USERLEN</x:v>
+      </x:c>
+      <x:c r="B37" s="12" t="str">
+        <x:v>DataProvider</x:v>
+      </x:c>
+      <x:c r="C37" s="12" t="str">
+        <x:v>Варианты RegistrationUiTest.usernameBoundaries</x:v>
+      </x:c>
+      <x:c r="D37" s="12" t="str">
+        <x:v>См. лист DataProvider: строки 1–4</x:v>
+      </x:c>
+      <x:c r="E37" s="12" t="str">
+        <x:v>Базовые данные: TD-NO-SESSION. Значения паролей заменены описанием назначения или длины.</x:v>
+      </x:c>
+      <x:c r="F37" s="12" t="str">
+        <x:v>RegistrationUiTest.usernameBoundaries</x:v>
+      </x:c>
+      <x:c r="G37" s="12" t="str">
+        <x:v>UI-029</x:v>
+      </x:c>
+      <x:c r="H37" s="12" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" ht="78" customHeight="1">
+      <x:c r="A38" s="12" t="str">
+        <x:v>DP-U-REG-PASSLEN</x:v>
+      </x:c>
+      <x:c r="B38" s="12" t="str">
+        <x:v>DataProvider</x:v>
+      </x:c>
+      <x:c r="C38" s="12" t="str">
+        <x:v>Варианты RegistrationUiTest.passwordBoundaries</x:v>
+      </x:c>
+      <x:c r="D38" s="12" t="str">
+        <x:v>См. лист DataProvider: строки 1–4</x:v>
+      </x:c>
+      <x:c r="E38" s="12" t="str">
+        <x:v>Базовые данные: TD-NO-SESSION. Значения паролей заменены описанием назначения или длины.</x:v>
+      </x:c>
+      <x:c r="F38" s="12" t="str">
+        <x:v>RegistrationUiTest.passwordBoundaries</x:v>
+      </x:c>
+      <x:c r="G38" s="12" t="str">
+        <x:v>UI-030</x:v>
+      </x:c>
+      <x:c r="H38" s="12" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" ht="78" customHeight="1">
+      <x:c r="A39" s="12" t="str">
+        <x:v>DP-U-REG-EMAIL</x:v>
+      </x:c>
+      <x:c r="B39" s="12" t="str">
+        <x:v>DataProvider</x:v>
+      </x:c>
+      <x:c r="C39" s="12" t="str">
+        <x:v>Варианты RegistrationUiTest.invalidEmails</x:v>
+      </x:c>
+      <x:c r="D39" s="12" t="str">
+        <x:v>См. лист DataProvider: строки 1–4</x:v>
+      </x:c>
+      <x:c r="E39" s="12" t="str">
+        <x:v>Базовые данные: TD-EMAIL-BAD. Значения паролей заменены описанием назначения или длины.</x:v>
+      </x:c>
+      <x:c r="F39" s="12" t="str">
+        <x:v>RegistrationUiTest.invalidEmails</x:v>
+      </x:c>
+      <x:c r="G39" s="12" t="str">
+        <x:v>UI-003</x:v>
+      </x:c>
+      <x:c r="H39" s="12" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" ht="78" customHeight="1">
+      <x:c r="A40" s="12" t="str">
+        <x:v>DP-U-REG-DUP</x:v>
+      </x:c>
+      <x:c r="B40" s="12" t="str">
+        <x:v>DataProvider</x:v>
+      </x:c>
+      <x:c r="C40" s="12" t="str">
+        <x:v>Варианты RegistrationUiTest.duplicateRegistrationData</x:v>
+      </x:c>
+      <x:c r="D40" s="12" t="str">
+        <x:v>См. лист DataProvider: строки 1–3</x:v>
+      </x:c>
+      <x:c r="E40" s="12" t="str">
+        <x:v>Базовые данные: TD-USER-NEW, TD-USER-EXIST. Значения паролей заменены описанием назначения или длины.</x:v>
+      </x:c>
+      <x:c r="F40" s="12" t="str">
+        <x:v>RegistrationUiTest.duplicateRegistrationData</x:v>
+      </x:c>
+      <x:c r="G40" s="12" t="str">
+        <x:v>UI-002, UI-021, UI-040</x:v>
+      </x:c>
+      <x:c r="H40" s="12" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" ht="78" customHeight="1">
+      <x:c r="A41" s="12" t="str">
+        <x:v>DP-U-TASK-FIELDS</x:v>
+      </x:c>
+      <x:c r="B41" s="12" t="str">
+        <x:v>DataProvider</x:v>
+      </x:c>
+      <x:c r="C41" s="12" t="str">
+        <x:v>Варианты TaskUiTest.taskData</x:v>
+      </x:c>
+      <x:c r="D41" s="12" t="str">
+        <x:v>См. лист DataProvider: строки 1–3</x:v>
+      </x:c>
+      <x:c r="E41" s="12" t="str">
+        <x:v>Базовые данные: TD-USER-A, TD-TASK-FULL. Значения паролей заменены описанием назначения или длины.</x:v>
+      </x:c>
+      <x:c r="F41" s="12" t="str">
+        <x:v>TaskUiTest.taskData</x:v>
+      </x:c>
+      <x:c r="G41" s="12" t="str">
+        <x:v>UI-035</x:v>
+      </x:c>
+      <x:c r="H41" s="12" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" ht="78" customHeight="1">
+      <x:c r="A42" s="12" t="str">
+        <x:v>DP-U-TASK-BADTITLE</x:v>
+      </x:c>
+      <x:c r="B42" s="12" t="str">
+        <x:v>DataProvider</x:v>
+      </x:c>
+      <x:c r="C42" s="12" t="str">
+        <x:v>Варианты TaskUiTest.invalidTaskTitles</x:v>
+      </x:c>
+      <x:c r="D42" s="12" t="str">
+        <x:v>См. лист DataProvider: строки 1–2</x:v>
+      </x:c>
+      <x:c r="E42" s="12" t="str">
+        <x:v>Базовые данные: TD-USER-A. Значения паролей заменены описанием назначения или длины.</x:v>
+      </x:c>
+      <x:c r="F42" s="12" t="str">
+        <x:v>TaskUiTest.invalidTaskTitles</x:v>
+      </x:c>
+      <x:c r="G42" s="12" t="str">
+        <x:v>UI-036</x:v>
+      </x:c>
+      <x:c r="H42" s="12" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" ht="78" customHeight="1">
+      <x:c r="A43" s="12" t="str">
+        <x:v>DP-U-TASK-TITLELEN</x:v>
+      </x:c>
+      <x:c r="B43" s="12" t="str">
+        <x:v>DataProvider</x:v>
+      </x:c>
+      <x:c r="C43" s="12" t="str">
+        <x:v>Варианты TaskUiTest.validTaskTitleLengths</x:v>
+      </x:c>
+      <x:c r="D43" s="12" t="str">
+        <x:v>См. лист DataProvider: строки 1–4</x:v>
+      </x:c>
+      <x:c r="E43" s="12" t="str">
+        <x:v>Базовые данные: TD-USER-A. Значения паролей заменены описанием назначения или длины.</x:v>
+      </x:c>
+      <x:c r="F43" s="12" t="str">
+        <x:v>TaskUiTest.validTaskTitleLengths</x:v>
+      </x:c>
+      <x:c r="G43" s="12" t="str">
+        <x:v>UI-037</x:v>
+      </x:c>
+      <x:c r="H43" s="12" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" ht="78" customHeight="1">
+      <x:c r="A44" s="12" t="str">
+        <x:v>DP-U-TASK-DESCLEN</x:v>
+      </x:c>
+      <x:c r="B44" s="12" t="str">
+        <x:v>DataProvider</x:v>
+      </x:c>
+      <x:c r="C44" s="12" t="str">
+        <x:v>Варианты TaskUiTest.taskDescriptionLengths</x:v>
+      </x:c>
+      <x:c r="D44" s="12" t="str">
+        <x:v>См. лист DataProvider: строки 1–5</x:v>
+      </x:c>
+      <x:c r="E44" s="12" t="str">
+        <x:v>Базовые данные: TD-USER-A, TD-TASK-FULL. Значения паролей заменены описанием назначения или длины.</x:v>
+      </x:c>
+      <x:c r="F44" s="12" t="str">
+        <x:v>TaskUiTest.taskDescriptionLengths</x:v>
+      </x:c>
+      <x:c r="G44" s="12" t="str">
+        <x:v>UI-038</x:v>
+      </x:c>
+      <x:c r="H44" s="12" t="n">
+        <x:v>5</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R68bf557348d14c81"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9b585bc2ba2442d5"/>
+  </x:tableParts>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="29" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="26" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="57" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="10" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="67" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="70" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="20" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="12" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="85" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="38" customHeight="1">
+      <x:c r="A1" s="13" t="str">
+        <x:v>ID строки</x:v>
+      </x:c>
+      <x:c r="B1" s="13" t="str">
+        <x:v>ID набора</x:v>
+      </x:c>
+      <x:c r="C1" s="13" t="str">
+        <x:v>Java-класс / DataProvider</x:v>
+      </x:c>
+      <x:c r="D1" s="13" t="str">
+        <x:v>Вариант</x:v>
+      </x:c>
+      <x:c r="E1" s="13" t="str">
+        <x:v>Данные без секретов</x:v>
+      </x:c>
+      <x:c r="F1" s="13" t="str">
+        <x:v>Ожидаемый результат</x:v>
+      </x:c>
+      <x:c r="G1" s="13" t="str">
+        <x:v>Актуальный кейс</x:v>
+      </x:c>
+      <x:c r="H1" s="13" t="str">
+        <x:v>Статус</x:v>
+      </x:c>
+      <x:c r="I1" s="13" t="str">
+        <x:v>Подтверждение запуска</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="64" customHeight="1">
+      <x:c r="A2" s="12" t="str">
+        <x:v>DP-A-REG-EMAIL-01</x:v>
+      </x:c>
+      <x:c r="B2" s="12" t="str">
+        <x:v>DP-A-REG-EMAIL</x:v>
+      </x:c>
+      <x:c r="C2" s="12" t="str">
+        <x:v>RegistrationTest.invalidEmails</x:v>
+      </x:c>
+      <x:c r="D2" s="12" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E2" s="12" t="str">
+        <x:v>invalid-email</x:v>
+      </x:c>
+      <x:c r="F2" s="12" t="str">
+        <x:v>400; validation schema; errors.email</x:v>
+      </x:c>
+      <x:c r="G2" s="12" t="str">
+        <x:v>API-003</x:v>
+      </x:c>
+      <x:c r="H2" s="12" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="I2" s="12" t="str">
+        <x:v>target/runs/ApiRegression/allure-results/52cd84e2-cd37-417a-b307-be53389d9517-result.json</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="64" customHeight="1">
+      <x:c r="A3" s="12" t="str">
+        <x:v>DP-A-REG-EMAIL-02</x:v>
+      </x:c>
+      <x:c r="B3" s="12" t="str">
+        <x:v>DP-A-REG-EMAIL</x:v>
+      </x:c>
+      <x:c r="C3" s="12" t="str">
+        <x:v>RegistrationTest.invalidEmails</x:v>
+      </x:c>
+      <x:c r="D3" s="12" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E3" s="12" t="str">
+        <x:v>user@</x:v>
+      </x:c>
+      <x:c r="F3" s="12" t="str">
+        <x:v>400; validation schema; errors.email</x:v>
+      </x:c>
+      <x:c r="G3" s="12" t="str">
+        <x:v>API-003</x:v>
+      </x:c>
+      <x:c r="H3" s="12" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="I3" s="12" t="str">
+        <x:v>target/runs/ApiRegression/allure-results/b8135696-f48a-46a8-9d0f-97a3d7578550-result.json</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="64" customHeight="1">
+      <x:c r="A4" s="12" t="str">
+        <x:v>DP-A-REG-EMAIL-03</x:v>
+      </x:c>
+      <x:c r="B4" s="12" t="str">
+        <x:v>DP-A-REG-EMAIL</x:v>
+      </x:c>
+      <x:c r="C4" s="12" t="str">
+        <x:v>RegistrationTest.invalidEmails</x:v>
+      </x:c>
+      <x:c r="D4" s="12" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E4" s="12" t="str">
+        <x:v>@example.com</x:v>
+      </x:c>
+      <x:c r="F4" s="12" t="str">
+        <x:v>400; validation schema; errors.email</x:v>
+      </x:c>
+      <x:c r="G4" s="12" t="str">
+        <x:v>API-003</x:v>
+      </x:c>
+      <x:c r="H4" s="12" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="I4" s="12" t="str">
+        <x:v>target/runs/ApiRegression/allure-results/a6eab156-4398-4d3d-be52-21d6cf83e16a-result.json</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="64" customHeight="1">
+      <x:c r="A5" s="12" t="str">
+        <x:v>DP-A-REG-EMPTY-01</x:v>
+      </x:c>
+      <x:c r="B5" s="12" t="str">
+        <x:v>DP-A-REG-EMPTY</x:v>
+      </x:c>
+      <x:c r="C5" s="12" t="str">
+        <x:v>RegistrationTest.emptyRequiredFields</x:v>
+      </x:c>
+      <x:c r="D5" s="12" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E5" s="12" t="str">
+        <x:v>username пуст; остальные поля валидны</x:v>
+      </x:c>
+      <x:c r="F5" s="12" t="str">
+        <x:v>400; validation schema; errors.username: «Логин не может быть пустым»</x:v>
+      </x:c>
+      <x:c r="G5" s="12" t="str">
+        <x:v>API-004</x:v>
+      </x:c>
+      <x:c r="H5" s="12" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="I5" s="12" t="str">
+        <x:v>target/runs/ApiRegression/allure-results/33f1e126-2f73-4378-869b-e83983bd6001-result.json</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="64" customHeight="1">
+      <x:c r="A6" s="12" t="str">
+        <x:v>DP-A-REG-EMPTY-02</x:v>
+      </x:c>
+      <x:c r="B6" s="12" t="str">
+        <x:v>DP-A-REG-EMPTY</x:v>
+      </x:c>
+      <x:c r="C6" s="12" t="str">
+        <x:v>RegistrationTest.emptyRequiredFields</x:v>
+      </x:c>
+      <x:c r="D6" s="12" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E6" s="12" t="str">
+        <x:v>email пуст; остальные поля валидны</x:v>
+      </x:c>
+      <x:c r="F6" s="12" t="str">
+        <x:v>400; validation schema; errors.email: «Email не может быть пустым»</x:v>
+      </x:c>
+      <x:c r="G6" s="12" t="str">
+        <x:v>API-004</x:v>
+      </x:c>
+      <x:c r="H6" s="12" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="I6" s="12" t="str">
+        <x:v>target/runs/ApiRegression/allure-results/7f4633aa-6d62-4d66-bbb7-3143d3e95582-result.json</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="64" customHeight="1">
+      <x:c r="A7" s="12" t="str">
+        <x:v>DP-A-REG-EMPTY-03</x:v>
+      </x:c>
+      <x:c r="B7" s="12" t="str">
+        <x:v>DP-A-REG-EMPTY</x:v>
+      </x:c>
+      <x:c r="C7" s="12" t="str">
+        <x:v>RegistrationTest.emptyRequiredFields</x:v>
+      </x:c>
+      <x:c r="D7" s="12" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E7" s="12" t="str">
+        <x:v>password пуст; остальные поля валидны</x:v>
+      </x:c>
+      <x:c r="F7" s="12" t="str">
+        <x:v>400; validation schema; errors.password: «Пароль не может быть пустым»</x:v>
+      </x:c>
+      <x:c r="G7" s="12" t="str">
+        <x:v>API-004</x:v>
+      </x:c>
+      <x:c r="H7" s="12" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="I7" s="12" t="str">
+        <x:v>target/runs/ApiRegression/allure-results/40190ef7-6d46-4f91-98ef-942151135824-result.json</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="64" customHeight="1">
+      <x:c r="A8" s="12" t="str">
+        <x:v>DP-A-REG-USERLEN-01</x:v>
+      </x:c>
+      <x:c r="B8" s="12" t="str">
+        <x:v>DP-A-REG-USERLEN</x:v>
+      </x:c>
+      <x:c r="C8" s="12" t="str">
+        <x:v>RegistrationTest.usernameBoundaries</x:v>
+      </x:c>
+      <x:c r="D8" s="12" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E8" s="12" t="str">
+        <x:v>Длина логина 2</x:v>
+      </x:c>
+      <x:c r="F8" s="12" t="str">
+        <x:v>400; validation schema; errors.username: длина 3–30; пользователя в БД нет</x:v>
+      </x:c>
+      <x:c r="G8" s="12" t="str">
+        <x:v>API-026</x:v>
+      </x:c>
+      <x:c r="H8" s="12" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="I8" s="12" t="str">
+        <x:v>target/runs/ApiRegression/allure-results/988ef23b-d092-4286-a93f-922952c439c2-result.json</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="64" customHeight="1">
+      <x:c r="A9" s="12" t="str">
+        <x:v>DP-A-REG-USERLEN-02</x:v>
+      </x:c>
+      <x:c r="B9" s="12" t="str">
+        <x:v>DP-A-REG-USERLEN</x:v>
+      </x:c>
+      <x:c r="C9" s="12" t="str">
+        <x:v>RegistrationTest.usernameBoundaries</x:v>
+      </x:c>
+      <x:c r="D9" s="12" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E9" s="12" t="str">
+        <x:v>Длина логина 3</x:v>
+      </x:c>
+      <x:c r="F9" s="12" t="str">
+        <x:v>201; «Пользователь зарегистрирован»; пользователь есть в БД</x:v>
+      </x:c>
+      <x:c r="G9" s="12" t="str">
+        <x:v>API-041</x:v>
+      </x:c>
+      <x:c r="H9" s="12" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="I9" s="12" t="str">
+        <x:v>target/runs/ApiRegression/allure-results/744cea1e-c81c-4c0a-95d8-83dd9a63d77b-result.json</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="64" customHeight="1">
+      <x:c r="A10" s="12" t="str">
+        <x:v>DP-A-REG-USERLEN-03</x:v>
+      </x:c>
+      <x:c r="B10" s="12" t="str">
+        <x:v>DP-A-REG-USERLEN</x:v>
+      </x:c>
+      <x:c r="C10" s="12" t="str">
+        <x:v>RegistrationTest.usernameBoundaries</x:v>
+      </x:c>
+      <x:c r="D10" s="12" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E10" s="12" t="str">
+        <x:v>Длина логина 30</x:v>
+      </x:c>
+      <x:c r="F10" s="12" t="str">
+        <x:v>201; «Пользователь зарегистрирован»; пользователь есть в БД</x:v>
+      </x:c>
+      <x:c r="G10" s="12" t="str">
+        <x:v>API-041</x:v>
+      </x:c>
+      <x:c r="H10" s="12" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="I10" s="12" t="str">
+        <x:v>target/runs/ApiRegression/allure-results/6897a01a-9a44-4ed8-878d-42493b5cd993-result.json</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="64" customHeight="1">
+      <x:c r="A11" s="12" t="str">
+        <x:v>DP-A-REG-USERLEN-04</x:v>
+      </x:c>
+      <x:c r="B11" s="12" t="str">
+        <x:v>DP-A-REG-USERLEN</x:v>
+      </x:c>
+      <x:c r="C11" s="12" t="str">
+        <x:v>RegistrationTest.usernameBoundaries</x:v>
+      </x:c>
+      <x:c r="D11" s="12" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E11" s="12" t="str">
+        <x:v>Длина логина 31</x:v>
+      </x:c>
+      <x:c r="F11" s="12" t="str">
+        <x:v>400; validation schema; errors.username: длина 3–30; пользователя в БД нет</x:v>
+      </x:c>
+      <x:c r="G11" s="12" t="str">
+        <x:v>API-028</x:v>
+      </x:c>
+      <x:c r="H11" s="12" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="I11" s="12" t="str">
+        <x:v>target/runs/ApiRegression/allure-results/1e6e9b19-a6d8-45e9-9b15-d89ae8b89821-result.json</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="64" customHeight="1">
+      <x:c r="A12" s="12" t="str">
+        <x:v>DP-A-REG-PASSLEN-01</x:v>
+      </x:c>
+      <x:c r="B12" s="12" t="str">
+        <x:v>DP-A-REG-PASSLEN</x:v>
+      </x:c>
+      <x:c r="C12" s="12" t="str">
+        <x:v>RegistrationTest.passwordBoundaries</x:v>
+      </x:c>
+      <x:c r="D12" s="12" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E12" s="12" t="str">
+        <x:v>Длина синтетического пароля 7</x:v>
+      </x:c>
+      <x:c r="F12" s="12" t="str">
+        <x:v>400; validation schema; errors.password: длина 8–72; пользователя в БД нет</x:v>
+      </x:c>
+      <x:c r="G12" s="12" t="str">
+        <x:v>API-027</x:v>
+      </x:c>
+      <x:c r="H12" s="12" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="I12" s="12" t="str">
+        <x:v>target/runs/ApiRegression/allure-results/de428496-a4f7-48c3-b755-b5df830c380b-result.json</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="64" customHeight="1">
+      <x:c r="A13" s="12" t="str">
+        <x:v>DP-A-REG-PASSLEN-02</x:v>
+      </x:c>
+      <x:c r="B13" s="12" t="str">
+        <x:v>DP-A-REG-PASSLEN</x:v>
+      </x:c>
+      <x:c r="C13" s="12" t="str">
+        <x:v>RegistrationTest.passwordBoundaries</x:v>
+      </x:c>
+      <x:c r="D13" s="12" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E13" s="12" t="str">
+        <x:v>Длина синтетического пароля 8</x:v>
+      </x:c>
+      <x:c r="F13" s="12" t="str">
+        <x:v>201; «Пользователь зарегистрирован»; пользователь есть в БД</x:v>
+      </x:c>
+      <x:c r="G13" s="12" t="str">
+        <x:v>API-042</x:v>
+      </x:c>
+      <x:c r="H13" s="12" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="I13" s="12" t="str">
+        <x:v>target/runs/ApiRegression/allure-results/2191dd4b-bc72-455c-b90f-e96a7e97b039-result.json</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="64" customHeight="1">
+      <x:c r="A14" s="12" t="str">
+        <x:v>DP-A-REG-PASSLEN-03</x:v>
+      </x:c>
+      <x:c r="B14" s="12" t="str">
+        <x:v>DP-A-REG-PASSLEN</x:v>
+      </x:c>
+      <x:c r="C14" s="12" t="str">
+        <x:v>RegistrationTest.passwordBoundaries</x:v>
+      </x:c>
+      <x:c r="D14" s="12" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E14" s="12" t="str">
+        <x:v>Длина синтетического пароля 72</x:v>
+      </x:c>
+      <x:c r="F14" s="12" t="str">
+        <x:v>201; «Пользователь зарегистрирован»; пользователь есть в БД</x:v>
+      </x:c>
+      <x:c r="G14" s="12" t="str">
+        <x:v>API-042</x:v>
+      </x:c>
+      <x:c r="H14" s="12" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="I14" s="12" t="str">
+        <x:v>target/runs/ApiRegression/allure-results/814ad178-e799-4955-ba5d-7da502fa4ea5-result.json</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="64" customHeight="1">
+      <x:c r="A15" s="12" t="str">
+        <x:v>DP-A-REG-PASSLEN-04</x:v>
+      </x:c>
+      <x:c r="B15" s="12" t="str">
+        <x:v>DP-A-REG-PASSLEN</x:v>
+      </x:c>
+      <x:c r="C15" s="12" t="str">
+        <x:v>RegistrationTest.passwordBoundaries</x:v>
+      </x:c>
+      <x:c r="D15" s="12" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E15" s="12" t="str">
+        <x:v>Длина синтетического пароля 73</x:v>
+      </x:c>
+      <x:c r="F15" s="12" t="str">
+        <x:v>400; validation schema; errors.password: длина 8–72; пользователя в БД нет</x:v>
+      </x:c>
+      <x:c r="G15" s="12" t="str">
+        <x:v>API-043</x:v>
+      </x:c>
+      <x:c r="H15" s="12" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="I15" s="12" t="str">
+        <x:v>target/runs/ApiRegression/allure-results/d97cc626-4cb2-4177-9110-bbc40338e154-result.json</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="64" customHeight="1">
+      <x:c r="A16" s="12" t="str">
+        <x:v>DP-A-TASK-BADTITLE-01</x:v>
+      </x:c>
+      <x:c r="B16" s="12" t="str">
+        <x:v>DP-A-TASK-BADTITLE</x:v>
+      </x:c>
+      <x:c r="C16" s="12" t="str">
+        <x:v>TaskApiTest.invalidTaskTitles</x:v>
+      </x:c>
+      <x:c r="D16" s="12" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E16" s="12" t="str">
+        <x:v>Название пусто; описание проверки; TODO/MEDIUM; deadline=NULL</x:v>
+      </x:c>
+      <x:c r="F16" s="12" t="str">
+        <x:v>400</x:v>
+      </x:c>
+      <x:c r="G16" s="12" t="str">
+        <x:v>API-009</x:v>
+      </x:c>
+      <x:c r="H16" s="12" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="I16" s="12" t="str">
+        <x:v>target/runs/ApiRegression/allure-results/9a20f7e8-2638-42ad-9163-9625cd0094c6-result.json</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="64" customHeight="1">
+      <x:c r="A17" s="12" t="str">
+        <x:v>DP-A-TASK-BADTITLE-02</x:v>
+      </x:c>
+      <x:c r="B17" s="12" t="str">
+        <x:v>DP-A-TASK-BADTITLE</x:v>
+      </x:c>
+      <x:c r="C17" s="12" t="str">
+        <x:v>TaskApiTest.invalidTaskTitles</x:v>
+      </x:c>
+      <x:c r="D17" s="12" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E17" s="12" t="str">
+        <x:v>Название длиной 2; описание проверки; TODO/MEDIUM; deadline=NULL</x:v>
+      </x:c>
+      <x:c r="F17" s="12" t="str">
+        <x:v>400</x:v>
+      </x:c>
+      <x:c r="G17" s="12" t="str">
+        <x:v>API-044</x:v>
+      </x:c>
+      <x:c r="H17" s="12" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="I17" s="12" t="str">
+        <x:v>target/runs/ApiRegression/allure-results/812736ce-3181-49a2-834f-b5d5e4a869f4-result.json</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="64" customHeight="1">
+      <x:c r="A18" s="12" t="str">
+        <x:v>DP-A-TASK-BADTITLE-03</x:v>
+      </x:c>
+      <x:c r="B18" s="12" t="str">
+        <x:v>DP-A-TASK-BADTITLE</x:v>
+      </x:c>
+      <x:c r="C18" s="12" t="str">
+        <x:v>TaskApiTest.invalidTaskTitles</x:v>
+      </x:c>
+      <x:c r="D18" s="12" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E18" s="12" t="str">
+        <x:v>Название длиной 101; описание проверки; TODO/MEDIUM; deadline=NULL</x:v>
+      </x:c>
+      <x:c r="F18" s="12" t="str">
+        <x:v>400</x:v>
+      </x:c>
+      <x:c r="G18" s="12" t="str">
+        <x:v>API-029</x:v>
+      </x:c>
+      <x:c r="H18" s="12" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="I18" s="12" t="str">
+        <x:v>target/runs/ApiRegression/allure-results/27f2326d-d138-450f-b696-d07cc46d57e0-result.json</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="64" customHeight="1">
+      <x:c r="A19" s="12" t="str">
+        <x:v>DP-A-TASK-TITLELEN-01</x:v>
+      </x:c>
+      <x:c r="B19" s="12" t="str">
+        <x:v>DP-A-TASK-TITLELEN</x:v>
+      </x:c>
+      <x:c r="C19" s="12" t="str">
+        <x:v>TaskApiTest.validTaskTitleBoundaries</x:v>
+      </x:c>
+      <x:c r="D19" s="12" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E19" s="12" t="str">
+        <x:v>Название длиной 3; описание проверки границ; TODO/MEDIUM; deadline=NULL</x:v>
+      </x:c>
+      <x:c r="F19" s="12" t="str">
+        <x:v>200; schema; title и запись в БД</x:v>
+      </x:c>
+      <x:c r="G19" s="12" t="str">
+        <x:v>API-037</x:v>
+      </x:c>
+      <x:c r="H19" s="12" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="I19" s="12" t="str">
+        <x:v>target/runs/ApiRegression/allure-results/43a7cfb4-b7fd-43bb-9270-2371e125531e-result.json</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="64" customHeight="1">
+      <x:c r="A20" s="12" t="str">
+        <x:v>DP-A-TASK-TITLELEN-02</x:v>
+      </x:c>
+      <x:c r="B20" s="12" t="str">
+        <x:v>DP-A-TASK-TITLELEN</x:v>
+      </x:c>
+      <x:c r="C20" s="12" t="str">
+        <x:v>TaskApiTest.validTaskTitleBoundaries</x:v>
+      </x:c>
+      <x:c r="D20" s="12" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E20" s="12" t="str">
+        <x:v>Название длиной 100; описание проверки границ; TODO/MEDIUM; deadline=NULL</x:v>
+      </x:c>
+      <x:c r="F20" s="12" t="str">
+        <x:v>200; schema; title и запись в БД</x:v>
+      </x:c>
+      <x:c r="G20" s="12" t="str">
+        <x:v>API-037</x:v>
+      </x:c>
+      <x:c r="H20" s="12" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="I20" s="12" t="str">
+        <x:v>target/runs/ApiRegression/allure-results/ca738fb2-1e9f-4602-8d4c-2b2467a12612-result.json</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="64" customHeight="1">
+      <x:c r="A21" s="12" t="str">
+        <x:v>DP-A-TASK-STATUS-01</x:v>
+      </x:c>
+      <x:c r="B21" s="12" t="str">
+        <x:v>DP-A-TASK-STATUS</x:v>
+      </x:c>
+      <x:c r="C21" s="12" t="str">
+        <x:v>TaskApiTest.validTaskStatuses</x:v>
+      </x:c>
+      <x:c r="D21" s="12" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E21" s="12" t="str">
+        <x:v>TODO</x:v>
+      </x:c>
+      <x:c r="F21" s="12" t="str">
+        <x:v>200; task schema, ID&gt;0, статус в ответе/GET; запись в БД</x:v>
+      </x:c>
+      <x:c r="G21" s="12" t="str">
+        <x:v>API-038</x:v>
+      </x:c>
+      <x:c r="H21" s="12" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="I21" s="12" t="str">
+        <x:v>target/runs/ApiRegression/allure-results/2942a6fb-a10a-4a82-845e-be0c286412c6-result.json</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="64" customHeight="1">
+      <x:c r="A22" s="12" t="str">
+        <x:v>DP-A-TASK-STATUS-02</x:v>
+      </x:c>
+      <x:c r="B22" s="12" t="str">
+        <x:v>DP-A-TASK-STATUS</x:v>
+      </x:c>
+      <x:c r="C22" s="12" t="str">
+        <x:v>TaskApiTest.validTaskStatuses</x:v>
+      </x:c>
+      <x:c r="D22" s="12" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E22" s="12" t="str">
+        <x:v>IN_PROGRESS</x:v>
+      </x:c>
+      <x:c r="F22" s="12" t="str">
+        <x:v>200; task schema, ID&gt;0, статус в ответе/GET; запись в БД</x:v>
+      </x:c>
+      <x:c r="G22" s="12" t="str">
+        <x:v>API-038</x:v>
+      </x:c>
+      <x:c r="H22" s="12" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="I22" s="12" t="str">
+        <x:v>target/runs/ApiRegression/allure-results/80e51002-b06a-4281-ac7e-44750c21ebcc-result.json</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="64" customHeight="1">
+      <x:c r="A23" s="12" t="str">
+        <x:v>DP-A-TASK-STATUS-03</x:v>
+      </x:c>
+      <x:c r="B23" s="12" t="str">
+        <x:v>DP-A-TASK-STATUS</x:v>
+      </x:c>
+      <x:c r="C23" s="12" t="str">
+        <x:v>TaskApiTest.validTaskStatuses</x:v>
+      </x:c>
+      <x:c r="D23" s="12" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E23" s="12" t="str">
+        <x:v>DONE</x:v>
+      </x:c>
+      <x:c r="F23" s="12" t="str">
+        <x:v>200; task schema, ID&gt;0, статус в ответе/GET; запись в БД</x:v>
+      </x:c>
+      <x:c r="G23" s="12" t="str">
+        <x:v>API-038</x:v>
+      </x:c>
+      <x:c r="H23" s="12" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="I23" s="12" t="str">
+        <x:v>target/runs/ApiRegression/allure-results/012912aa-b647-4685-a414-02a6b25e9bfd-result.json</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="64" customHeight="1">
+      <x:c r="A24" s="12" t="str">
+        <x:v>DP-A-TASK-PRIORITY-01</x:v>
+      </x:c>
+      <x:c r="B24" s="12" t="str">
+        <x:v>DP-A-TASK-PRIORITY</x:v>
+      </x:c>
+      <x:c r="C24" s="12" t="str">
+        <x:v>TaskApiTest.validTaskPriorities</x:v>
+      </x:c>
+      <x:c r="D24" s="12" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E24" s="12" t="str">
+        <x:v>LOW</x:v>
+      </x:c>
+      <x:c r="F24" s="12" t="str">
+        <x:v>200; task schema, ID&gt;0, приоритет в ответе/GET; запись в БД</x:v>
+      </x:c>
+      <x:c r="G24" s="12" t="str">
+        <x:v>API-039</x:v>
+      </x:c>
+      <x:c r="H24" s="12" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="I24" s="12" t="str">
+        <x:v>target/runs/ApiRegression/allure-results/dc6224be-da50-405d-b5c3-fec9cf427cf3-result.json</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="64" customHeight="1">
+      <x:c r="A25" s="12" t="str">
+        <x:v>DP-A-TASK-PRIORITY-02</x:v>
+      </x:c>
+      <x:c r="B25" s="12" t="str">
+        <x:v>DP-A-TASK-PRIORITY</x:v>
+      </x:c>
+      <x:c r="C25" s="12" t="str">
+        <x:v>TaskApiTest.validTaskPriorities</x:v>
+      </x:c>
+      <x:c r="D25" s="12" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E25" s="12" t="str">
+        <x:v>MEDIUM</x:v>
+      </x:c>
+      <x:c r="F25" s="12" t="str">
+        <x:v>200; task schema, ID&gt;0, приоритет в ответе/GET; запись в БД</x:v>
+      </x:c>
+      <x:c r="G25" s="12" t="str">
+        <x:v>API-039</x:v>
+      </x:c>
+      <x:c r="H25" s="12" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="I25" s="12" t="str">
+        <x:v>target/runs/ApiRegression/allure-results/00de3d40-1645-42ed-9433-5bd80e8765af-result.json</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="64" customHeight="1">
+      <x:c r="A26" s="12" t="str">
+        <x:v>DP-A-TASK-PRIORITY-03</x:v>
+      </x:c>
+      <x:c r="B26" s="12" t="str">
+        <x:v>DP-A-TASK-PRIORITY</x:v>
+      </x:c>
+      <x:c r="C26" s="12" t="str">
+        <x:v>TaskApiTest.validTaskPriorities</x:v>
+      </x:c>
+      <x:c r="D26" s="12" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E26" s="12" t="str">
+        <x:v>HIGH</x:v>
+      </x:c>
+      <x:c r="F26" s="12" t="str">
+        <x:v>200; task schema, ID&gt;0, приоритет в ответе/GET; запись в БД</x:v>
+      </x:c>
+      <x:c r="G26" s="12" t="str">
+        <x:v>API-039</x:v>
+      </x:c>
+      <x:c r="H26" s="12" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="I26" s="12" t="str">
+        <x:v>target/runs/ApiRegression/allure-results/49b0429f-960a-42a8-8b79-bc6cbf5f366c-result.json</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="64" customHeight="1">
+      <x:c r="A27" s="12" t="str">
+        <x:v>DP-A-TASK-BADENUM-01</x:v>
+      </x:c>
+      <x:c r="B27" s="12" t="str">
+        <x:v>DP-A-TASK-BADENUM</x:v>
+      </x:c>
+      <x:c r="C27" s="12" t="str">
+        <x:v>TaskApiTest.invalidTaskEnums</x:v>
+      </x:c>
+      <x:c r="D27" s="12" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E27" s="12" t="str">
+        <x:v>status=INVALID; priority=MEDIUM</x:v>
+      </x:c>
+      <x:c r="F27" s="12" t="str">
+        <x:v>400</x:v>
+      </x:c>
+      <x:c r="G27" s="12" t="str">
+        <x:v>API-030</x:v>
+      </x:c>
+      <x:c r="H27" s="12" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="I27" s="12" t="str">
+        <x:v>target/runs/ApiRegression/allure-results/88deafd5-384c-4e09-bf45-242a5291365a-result.json</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="64" customHeight="1">
+      <x:c r="A28" s="12" t="str">
+        <x:v>DP-A-TASK-BADENUM-02</x:v>
+      </x:c>
+      <x:c r="B28" s="12" t="str">
+        <x:v>DP-A-TASK-BADENUM</x:v>
+      </x:c>
+      <x:c r="C28" s="12" t="str">
+        <x:v>TaskApiTest.invalidTaskEnums</x:v>
+      </x:c>
+      <x:c r="D28" s="12" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E28" s="12" t="str">
+        <x:v>status=TODO; priority=INVALID</x:v>
+      </x:c>
+      <x:c r="F28" s="12" t="str">
+        <x:v>400</x:v>
+      </x:c>
+      <x:c r="G28" s="12" t="str">
+        <x:v>API-031</x:v>
+      </x:c>
+      <x:c r="H28" s="12" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="I28" s="12" t="str">
+        <x:v>target/runs/ApiRegression/allure-results/81670d16-5015-4ef9-9d7a-fe55de6b643a-result.json</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="64" customHeight="1">
+      <x:c r="A29" s="12" t="str">
+        <x:v>DP-A-TASK-BADENUM-03</x:v>
+      </x:c>
+      <x:c r="B29" s="12" t="str">
+        <x:v>DP-A-TASK-BADENUM</x:v>
+      </x:c>
+      <x:c r="C29" s="12" t="str">
+        <x:v>TaskApiTest.invalidTaskEnums</x:v>
+      </x:c>
+      <x:c r="D29" s="12" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E29" s="12" t="str">
+        <x:v>status пуст; priority=MEDIUM</x:v>
+      </x:c>
+      <x:c r="F29" s="12" t="str">
+        <x:v>400</x:v>
+      </x:c>
+      <x:c r="G29" s="12" t="str">
+        <x:v>API-030</x:v>
+      </x:c>
+      <x:c r="H29" s="12" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="I29" s="12" t="str">
+        <x:v>target/runs/ApiRegression/allure-results/c3e4d7b4-9125-4ee6-a02a-32820a6dfb93-result.json</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="64" customHeight="1">
+      <x:c r="A30" s="12" t="str">
+        <x:v>DP-A-TASK-BADENUM-04</x:v>
+      </x:c>
+      <x:c r="B30" s="12" t="str">
+        <x:v>DP-A-TASK-BADENUM</x:v>
+      </x:c>
+      <x:c r="C30" s="12" t="str">
+        <x:v>TaskApiTest.invalidTaskEnums</x:v>
+      </x:c>
+      <x:c r="D30" s="12" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E30" s="12" t="str">
+        <x:v>status=TODO; priority пуст</x:v>
+      </x:c>
+      <x:c r="F30" s="12" t="str">
+        <x:v>400</x:v>
+      </x:c>
+      <x:c r="G30" s="12" t="str">
+        <x:v>API-031</x:v>
+      </x:c>
+      <x:c r="H30" s="12" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="I30" s="12" t="str">
+        <x:v>target/runs/ApiRegression/allure-results/1bf3ecf3-0ed8-4aa9-b600-2444eac31203-result.json</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="64" customHeight="1">
+      <x:c r="A31" s="12" t="str">
+        <x:v>DP-A-TASK-BADUPDATE-01</x:v>
+      </x:c>
+      <x:c r="B31" s="12" t="str">
+        <x:v>DP-A-TASK-BADUPDATE</x:v>
+      </x:c>
+      <x:c r="C31" s="12" t="str">
+        <x:v>TaskApiTest.invalidTaskUpdateData</x:v>
+      </x:c>
+      <x:c r="D31" s="12" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E31" s="12" t="str">
+        <x:v>title пуст</x:v>
+      </x:c>
+      <x:c r="F31" s="12" t="str">
+        <x:v>PUT 400; GET 200, task schema; исходные поля неизменны</x:v>
+      </x:c>
+      <x:c r="G31" s="12" t="str">
+        <x:v>API-040</x:v>
+      </x:c>
+      <x:c r="H31" s="12" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="I31" s="12" t="str">
+        <x:v>target/runs/ApiRegression/allure-results/472e938f-70b9-43b5-8f88-c5f976d90778-result.json</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="64" customHeight="1">
+      <x:c r="A32" s="12" t="str">
+        <x:v>DP-A-TASK-BADUPDATE-02</x:v>
+      </x:c>
+      <x:c r="B32" s="12" t="str">
+        <x:v>DP-A-TASK-BADUPDATE</x:v>
+      </x:c>
+      <x:c r="C32" s="12" t="str">
+        <x:v>TaskApiTest.invalidTaskUpdateData</x:v>
+      </x:c>
+      <x:c r="D32" s="12" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E32" s="12" t="str">
+        <x:v>title длиной 2</x:v>
+      </x:c>
+      <x:c r="F32" s="12" t="str">
+        <x:v>PUT 400; GET 200, task schema; исходные поля неизменны</x:v>
+      </x:c>
+      <x:c r="G32" s="12" t="str">
+        <x:v>API-040</x:v>
+      </x:c>
+      <x:c r="H32" s="12" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="I32" s="12" t="str">
+        <x:v>target/runs/ApiRegression/allure-results/19db9a70-91f1-4fe8-b964-0ec05cb39f20-result.json</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="64" customHeight="1">
+      <x:c r="A33" s="12" t="str">
+        <x:v>DP-A-TASK-BADUPDATE-03</x:v>
+      </x:c>
+      <x:c r="B33" s="12" t="str">
+        <x:v>DP-A-TASK-BADUPDATE</x:v>
+      </x:c>
+      <x:c r="C33" s="12" t="str">
+        <x:v>TaskApiTest.invalidTaskUpdateData</x:v>
+      </x:c>
+      <x:c r="D33" s="12" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E33" s="12" t="str">
+        <x:v>title длиной 101</x:v>
+      </x:c>
+      <x:c r="F33" s="12" t="str">
+        <x:v>PUT 400; GET 200, task schema; исходные поля неизменны</x:v>
+      </x:c>
+      <x:c r="G33" s="12" t="str">
+        <x:v>API-040</x:v>
+      </x:c>
+      <x:c r="H33" s="12" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="I33" s="12" t="str">
+        <x:v>target/runs/ApiRegression/allure-results/4219fc93-838a-4214-8f6a-dbe8b1faf2bd-result.json</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="64" customHeight="1">
+      <x:c r="A34" s="12" t="str">
+        <x:v>DP-A-TASK-BADUPDATE-04</x:v>
+      </x:c>
+      <x:c r="B34" s="12" t="str">
+        <x:v>DP-A-TASK-BADUPDATE</x:v>
+      </x:c>
+      <x:c r="C34" s="12" t="str">
+        <x:v>TaskApiTest.invalidTaskUpdateData</x:v>
+      </x:c>
+      <x:c r="D34" s="12" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E34" s="12" t="str">
+        <x:v>title=Valid title; status=INVALID</x:v>
+      </x:c>
+      <x:c r="F34" s="12" t="str">
+        <x:v>PUT 400; GET 200, task schema; исходные поля неизменны</x:v>
+      </x:c>
+      <x:c r="G34" s="12" t="str">
+        <x:v>API-040</x:v>
+      </x:c>
+      <x:c r="H34" s="12" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="I34" s="12" t="str">
+        <x:v>target/runs/ApiRegression/allure-results/512bd700-8347-484e-80b1-04ee848183f5-result.json</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="64" customHeight="1">
+      <x:c r="A35" s="12" t="str">
+        <x:v>DP-A-TASK-BADUPDATE-05</x:v>
+      </x:c>
+      <x:c r="B35" s="12" t="str">
+        <x:v>DP-A-TASK-BADUPDATE</x:v>
+      </x:c>
+      <x:c r="C35" s="12" t="str">
+        <x:v>TaskApiTest.invalidTaskUpdateData</x:v>
+      </x:c>
+      <x:c r="D35" s="12" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E35" s="12" t="str">
+        <x:v>title=Valid title; priority=INVALID</x:v>
+      </x:c>
+      <x:c r="F35" s="12" t="str">
+        <x:v>PUT 400; GET 200, task schema; исходные поля неизменны</x:v>
+      </x:c>
+      <x:c r="G35" s="12" t="str">
+        <x:v>API-040</x:v>
+      </x:c>
+      <x:c r="H35" s="12" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="I35" s="12" t="str">
+        <x:v>target/runs/ApiRegression/allure-results/a6f8b87d-0c1a-4b1a-ba68-38797b447408-result.json</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" ht="64" customHeight="1">
+      <x:c r="A36" s="12" t="str">
+        <x:v>DP-U-LOGIN-ELEMENT-01</x:v>
+      </x:c>
+      <x:c r="B36" s="12" t="str">
+        <x:v>DP-U-LOGIN-ELEMENT</x:v>
+      </x:c>
+      <x:c r="C36" s="12" t="str">
+        <x:v>LoginUiTest.loginElements</x:v>
+      </x:c>
+      <x:c r="D36" s="12" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E36" s="12" t="str">
+        <x:v>USERNAME</x:v>
+      </x:c>
+      <x:c r="F36" s="12" t="str">
+        <x:v>Элемент видим</x:v>
+      </x:c>
+      <x:c r="G36" s="12" t="str">
+        <x:v>UI-024</x:v>
+      </x:c>
+      <x:c r="H36" s="12" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="I36" s="12" t="str">
+        <x:v>target/runs/UiRegression/allure-results/4d1a70e5-8fdb-414c-94b0-9c52c70fbc78-result.json</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" ht="64" customHeight="1">
+      <x:c r="A37" s="12" t="str">
+        <x:v>DP-U-LOGIN-ELEMENT-02</x:v>
+      </x:c>
+      <x:c r="B37" s="12" t="str">
+        <x:v>DP-U-LOGIN-ELEMENT</x:v>
+      </x:c>
+      <x:c r="C37" s="12" t="str">
+        <x:v>LoginUiTest.loginElements</x:v>
+      </x:c>
+      <x:c r="D37" s="12" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E37" s="12" t="str">
+        <x:v>PASSWORD</x:v>
+      </x:c>
+      <x:c r="F37" s="12" t="str">
+        <x:v>Элемент видим</x:v>
+      </x:c>
+      <x:c r="G37" s="12" t="str">
+        <x:v>UI-024</x:v>
+      </x:c>
+      <x:c r="H37" s="12" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="I37" s="12" t="str">
+        <x:v>target/runs/UiRegression/allure-results/b19dc599-101b-4337-a9a5-5c37337bf2e1-result.json</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" ht="64" customHeight="1">
+      <x:c r="A38" s="12" t="str">
+        <x:v>DP-U-LOGIN-ELEMENT-03</x:v>
+      </x:c>
+      <x:c r="B38" s="12" t="str">
+        <x:v>DP-U-LOGIN-ELEMENT</x:v>
+      </x:c>
+      <x:c r="C38" s="12" t="str">
+        <x:v>LoginUiTest.loginElements</x:v>
+      </x:c>
+      <x:c r="D38" s="12" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E38" s="12" t="str">
+        <x:v>LOGIN_BUTTON</x:v>
+      </x:c>
+      <x:c r="F38" s="12" t="str">
+        <x:v>Элемент видим</x:v>
+      </x:c>
+      <x:c r="G38" s="12" t="str">
+        <x:v>UI-024</x:v>
+      </x:c>
+      <x:c r="H38" s="12" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="I38" s="12" t="str">
+        <x:v>target/runs/UiRegression/allure-results/40f5a979-dc4b-4af5-ae23-76bfcd082b35-result.json</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" ht="64" customHeight="1">
+      <x:c r="A39" s="12" t="str">
+        <x:v>DP-U-LOGIN-ELEMENT-04</x:v>
+      </x:c>
+      <x:c r="B39" s="12" t="str">
+        <x:v>DP-U-LOGIN-ELEMENT</x:v>
+      </x:c>
+      <x:c r="C39" s="12" t="str">
+        <x:v>LoginUiTest.loginElements</x:v>
+      </x:c>
+      <x:c r="D39" s="12" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E39" s="12" t="str">
+        <x:v>REGISTRATION_LINK</x:v>
+      </x:c>
+      <x:c r="F39" s="12" t="str">
+        <x:v>Элемент видим</x:v>
+      </x:c>
+      <x:c r="G39" s="12" t="str">
+        <x:v>UI-024</x:v>
+      </x:c>
+      <x:c r="H39" s="12" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="I39" s="12" t="str">
+        <x:v>target/runs/UiRegression/allure-results/e46efeed-683b-4c6e-858b-044fd6a24678-result.json</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" ht="64" customHeight="1">
+      <x:c r="A40" s="12" t="str">
+        <x:v>DP-U-LOGIN-ELEMENT-05</x:v>
+      </x:c>
+      <x:c r="B40" s="12" t="str">
+        <x:v>DP-U-LOGIN-ELEMENT</x:v>
+      </x:c>
+      <x:c r="C40" s="12" t="str">
+        <x:v>LoginUiTest.loginElements</x:v>
+      </x:c>
+      <x:c r="D40" s="12" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E40" s="12" t="str">
+        <x:v>PAGE_TITLE</x:v>
+      </x:c>
+      <x:c r="F40" s="12" t="str">
+        <x:v>Элемент видим</x:v>
+      </x:c>
+      <x:c r="G40" s="12" t="str">
+        <x:v>UI-024</x:v>
+      </x:c>
+      <x:c r="H40" s="12" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="I40" s="12" t="str">
+        <x:v>target/runs/UiRegression/allure-results/e4bd5e95-b647-403a-8595-a4111e948873-result.json</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" ht="64" customHeight="1">
+      <x:c r="A41" s="12" t="str">
+        <x:v>DP-U-LOGIN-BAD-01</x:v>
+      </x:c>
+      <x:c r="B41" s="12" t="str">
+        <x:v>DP-U-LOGIN-BAD</x:v>
+      </x:c>
+      <x:c r="C41" s="12" t="str">
+        <x:v>LoginUiTest.invalidCredentials</x:v>
+      </x:c>
+      <x:c r="D41" s="12" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E41" s="12" t="str">
+        <x:v>Существующий логин; неверный пароль (значение не публикуется)</x:v>
+      </x:c>
+      <x:c r="F41" s="12" t="str">
+        <x:v>/login?error; «Неверный логин или пароль»</x:v>
+      </x:c>
+      <x:c r="G41" s="12" t="str">
+        <x:v>UI-006</x:v>
+      </x:c>
+      <x:c r="H41" s="12" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="I41" s="12" t="str">
+        <x:v>target/runs/UiRegression/allure-results/24835369-5d48-40d1-bcb2-0aeb15b31542-result.json</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" ht="64" customHeight="1">
+      <x:c r="A42" s="12" t="str">
+        <x:v>DP-U-LOGIN-BAD-02</x:v>
+      </x:c>
+      <x:c r="B42" s="12" t="str">
+        <x:v>DP-U-LOGIN-BAD</x:v>
+      </x:c>
+      <x:c r="C42" s="12" t="str">
+        <x:v>LoginUiTest.invalidCredentials</x:v>
+      </x:c>
+      <x:c r="D42" s="12" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E42" s="12" t="str">
+        <x:v>Неизвестный логин; неверный пароль (значение не публикуется)</x:v>
+      </x:c>
+      <x:c r="F42" s="12" t="str">
+        <x:v>/login?error; «Неверный логин или пароль»</x:v>
+      </x:c>
+      <x:c r="G42" s="12" t="str">
+        <x:v>UI-007</x:v>
+      </x:c>
+      <x:c r="H42" s="12" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="I42" s="12" t="str">
+        <x:v>target/runs/UiRegression/allure-results/2ff24881-3c0e-4c9e-8133-0cfff77943c3-result.json</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" ht="64" customHeight="1">
+      <x:c r="A43" s="12" t="str">
+        <x:v>DP-U-LOGIN-BAD-03</x:v>
+      </x:c>
+      <x:c r="B43" s="12" t="str">
+        <x:v>DP-U-LOGIN-BAD</x:v>
+      </x:c>
+      <x:c r="C43" s="12" t="str">
+        <x:v>LoginUiTest.invalidCredentials</x:v>
+      </x:c>
+      <x:c r="D43" s="12" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E43" s="12" t="str">
+        <x:v>Неизвестный логин; пароль из TEST_USER_PASSWORD (значение не публикуется)</x:v>
+      </x:c>
+      <x:c r="F43" s="12" t="str">
+        <x:v>/login?error; «Неверный логин или пароль»</x:v>
+      </x:c>
+      <x:c r="G43" s="12" t="str">
+        <x:v>UI-007</x:v>
+      </x:c>
+      <x:c r="H43" s="12" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="I43" s="12" t="str">
+        <x:v>target/runs/UiRegression/allure-results/2c5a5117-2549-41ac-ae00-f06864724a4c-result.json</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" ht="64" customHeight="1">
+      <x:c r="A44" s="12" t="str">
+        <x:v>DP-U-LOGIN-EMPTY-01</x:v>
+      </x:c>
+      <x:c r="B44" s="12" t="str">
+        <x:v>DP-U-LOGIN-EMPTY</x:v>
+      </x:c>
+      <x:c r="C44" s="12" t="str">
+        <x:v>LoginUiTest.emptyCredentials</x:v>
+      </x:c>
+      <x:c r="D44" s="12" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E44" s="12" t="str">
+        <x:v>Логин пуст; пароль из окружения</x:v>
+      </x:c>
+      <x:c r="F44" s="12" t="str">
+        <x:v>valueMissing username; /login</x:v>
+      </x:c>
+      <x:c r="G44" s="12" t="str">
+        <x:v>UI-025</x:v>
+      </x:c>
+      <x:c r="H44" s="12" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="I44" s="12" t="str">
+        <x:v>target/runs/UiRegression/allure-results/6203f67f-399b-4dae-8780-af77eabcf673-result.json</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" ht="64" customHeight="1">
+      <x:c r="A45" s="12" t="str">
+        <x:v>DP-U-LOGIN-EMPTY-02</x:v>
+      </x:c>
+      <x:c r="B45" s="12" t="str">
+        <x:v>DP-U-LOGIN-EMPTY</x:v>
+      </x:c>
+      <x:c r="C45" s="12" t="str">
+        <x:v>LoginUiTest.emptyCredentials</x:v>
+      </x:c>
+      <x:c r="D45" s="12" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E45" s="12" t="str">
+        <x:v>Существующий логин; пароль пуст</x:v>
+      </x:c>
+      <x:c r="F45" s="12" t="str">
+        <x:v>valueMissing password; /login</x:v>
+      </x:c>
+      <x:c r="G45" s="12" t="str">
+        <x:v>UI-025</x:v>
+      </x:c>
+      <x:c r="H45" s="12" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="I45" s="12" t="str">
+        <x:v>target/runs/UiRegression/allure-results/a1d71b9c-42f0-4e8e-bdfc-c9118c86d74a-result.json</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" ht="64" customHeight="1">
+      <x:c r="A46" s="12" t="str">
+        <x:v>DP-U-LOGIN-EMPTY-03</x:v>
+      </x:c>
+      <x:c r="B46" s="12" t="str">
+        <x:v>DP-U-LOGIN-EMPTY</x:v>
+      </x:c>
+      <x:c r="C46" s="12" t="str">
+        <x:v>LoginUiTest.emptyCredentials</x:v>
+      </x:c>
+      <x:c r="D46" s="12" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E46" s="12" t="str">
+        <x:v>Логин и пароль пусты</x:v>
+      </x:c>
+      <x:c r="F46" s="12" t="str">
+        <x:v>valueMissing username; /login</x:v>
+      </x:c>
+      <x:c r="G46" s="12" t="str">
+        <x:v>UI-025</x:v>
+      </x:c>
+      <x:c r="H46" s="12" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="I46" s="12" t="str">
+        <x:v>target/runs/UiRegression/allure-results/69973129-6cce-44e8-9807-1901eaca2020-result.json</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" ht="64" customHeight="1">
+      <x:c r="A47" s="12" t="str">
+        <x:v>DP-U-REG-ELEMENT-01</x:v>
+      </x:c>
+      <x:c r="B47" s="12" t="str">
+        <x:v>DP-U-REG-ELEMENT</x:v>
+      </x:c>
+      <x:c r="C47" s="12" t="str">
+        <x:v>RegistrationUiTest.registrationElements</x:v>
+      </x:c>
+      <x:c r="D47" s="12" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E47" s="12" t="str">
+        <x:v>USERNAME</x:v>
+      </x:c>
+      <x:c r="F47" s="12" t="str">
+        <x:v>Элемент видим</x:v>
+      </x:c>
+      <x:c r="G47" s="12" t="str">
+        <x:v>UI-027</x:v>
+      </x:c>
+      <x:c r="H47" s="12" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="I47" s="12" t="str">
+        <x:v>target/runs/UiRegression/allure-results/e7553d98-302e-49a2-b404-43db0fa48405-result.json</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" ht="64" customHeight="1">
+      <x:c r="A48" s="12" t="str">
+        <x:v>DP-U-REG-ELEMENT-02</x:v>
+      </x:c>
+      <x:c r="B48" s="12" t="str">
+        <x:v>DP-U-REG-ELEMENT</x:v>
+      </x:c>
+      <x:c r="C48" s="12" t="str">
+        <x:v>RegistrationUiTest.registrationElements</x:v>
+      </x:c>
+      <x:c r="D48" s="12" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E48" s="12" t="str">
+        <x:v>EMAIL</x:v>
+      </x:c>
+      <x:c r="F48" s="12" t="str">
+        <x:v>Элемент видим</x:v>
+      </x:c>
+      <x:c r="G48" s="12" t="str">
+        <x:v>UI-027</x:v>
+      </x:c>
+      <x:c r="H48" s="12" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="I48" s="12" t="str">
+        <x:v>target/runs/UiRegression/allure-results/15c074d5-302d-4b86-ac95-e106cc1a57a4-result.json</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" ht="64" customHeight="1">
+      <x:c r="A49" s="12" t="str">
+        <x:v>DP-U-REG-ELEMENT-03</x:v>
+      </x:c>
+      <x:c r="B49" s="12" t="str">
+        <x:v>DP-U-REG-ELEMENT</x:v>
+      </x:c>
+      <x:c r="C49" s="12" t="str">
+        <x:v>RegistrationUiTest.registrationElements</x:v>
+      </x:c>
+      <x:c r="D49" s="12" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E49" s="12" t="str">
+        <x:v>PASSWORD</x:v>
+      </x:c>
+      <x:c r="F49" s="12" t="str">
+        <x:v>Элемент видим</x:v>
+      </x:c>
+      <x:c r="G49" s="12" t="str">
+        <x:v>UI-027</x:v>
+      </x:c>
+      <x:c r="H49" s="12" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="I49" s="12" t="str">
+        <x:v>target/runs/UiRegression/allure-results/b54cd318-73df-43d2-a9f0-07ff7403d976-result.json</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" ht="64" customHeight="1">
+      <x:c r="A50" s="12" t="str">
+        <x:v>DP-U-REG-ELEMENT-04</x:v>
+      </x:c>
+      <x:c r="B50" s="12" t="str">
+        <x:v>DP-U-REG-ELEMENT</x:v>
+      </x:c>
+      <x:c r="C50" s="12" t="str">
+        <x:v>RegistrationUiTest.registrationElements</x:v>
+      </x:c>
+      <x:c r="D50" s="12" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E50" s="12" t="str">
+        <x:v>REGISTER_BUTTON</x:v>
+      </x:c>
+      <x:c r="F50" s="12" t="str">
+        <x:v>Элемент видим</x:v>
+      </x:c>
+      <x:c r="G50" s="12" t="str">
+        <x:v>UI-027</x:v>
+      </x:c>
+      <x:c r="H50" s="12" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="I50" s="12" t="str">
+        <x:v>target/runs/UiRegression/allure-results/378658c7-384d-4918-bdb5-97cc8135c9ea-result.json</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" ht="64" customHeight="1">
+      <x:c r="A51" s="12" t="str">
+        <x:v>DP-U-REG-ELEMENT-05</x:v>
+      </x:c>
+      <x:c r="B51" s="12" t="str">
+        <x:v>DP-U-REG-ELEMENT</x:v>
+      </x:c>
+      <x:c r="C51" s="12" t="str">
+        <x:v>RegistrationUiTest.registrationElements</x:v>
+      </x:c>
+      <x:c r="D51" s="12" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E51" s="12" t="str">
+        <x:v>LOGIN_LINK</x:v>
+      </x:c>
+      <x:c r="F51" s="12" t="str">
+        <x:v>Элемент видим</x:v>
+      </x:c>
+      <x:c r="G51" s="12" t="str">
+        <x:v>UI-027</x:v>
+      </x:c>
+      <x:c r="H51" s="12" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="I51" s="12" t="str">
+        <x:v>target/runs/UiRegression/allure-results/4d69f132-fd23-43e2-a7a4-36d65b89f57e-result.json</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" ht="64" customHeight="1">
+      <x:c r="A52" s="12" t="str">
+        <x:v>DP-U-REG-ELEMENT-06</x:v>
+      </x:c>
+      <x:c r="B52" s="12" t="str">
+        <x:v>DP-U-REG-ELEMENT</x:v>
+      </x:c>
+      <x:c r="C52" s="12" t="str">
+        <x:v>RegistrationUiTest.registrationElements</x:v>
+      </x:c>
+      <x:c r="D52" s="12" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="E52" s="12" t="str">
+        <x:v>PAGE_TITLE</x:v>
+      </x:c>
+      <x:c r="F52" s="12" t="str">
+        <x:v>Элемент видим</x:v>
+      </x:c>
+      <x:c r="G52" s="12" t="str">
+        <x:v>UI-027</x:v>
+      </x:c>
+      <x:c r="H52" s="12" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="I52" s="12" t="str">
+        <x:v>target/runs/UiRegression/allure-results/edee04c2-bf55-494d-ac35-137abc2c40ea-result.json</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" ht="64" customHeight="1">
+      <x:c r="A53" s="12" t="str">
+        <x:v>DP-U-REG-EMPTY-01</x:v>
+      </x:c>
+      <x:c r="B53" s="12" t="str">
+        <x:v>DP-U-REG-EMPTY</x:v>
+      </x:c>
+      <x:c r="C53" s="12" t="str">
+        <x:v>RegistrationUiTest.emptyRegistrationFields</x:v>
+      </x:c>
+      <x:c r="D53" s="12" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E53" s="12" t="str">
+        <x:v>Логин пуст; email и пароль синтетически валидны</x:v>
+      </x:c>
+      <x:c r="F53" s="12" t="str">
+        <x:v>valueMissing username; /register</x:v>
+      </x:c>
+      <x:c r="G53" s="12" t="str">
+        <x:v>UI-004</x:v>
+      </x:c>
+      <x:c r="H53" s="12" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="I53" s="12" t="str">
+        <x:v>target/runs/UiRegression/allure-results/ece15759-6f3f-456d-b40c-b07fa58087ac-result.json</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" ht="64" customHeight="1">
+      <x:c r="A54" s="12" t="str">
+        <x:v>DP-U-REG-EMPTY-02</x:v>
+      </x:c>
+      <x:c r="B54" s="12" t="str">
+        <x:v>DP-U-REG-EMPTY</x:v>
+      </x:c>
+      <x:c r="C54" s="12" t="str">
+        <x:v>RegistrationUiTest.emptyRegistrationFields</x:v>
+      </x:c>
+      <x:c r="D54" s="12" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E54" s="12" t="str">
+        <x:v>Email пуст; логин и пароль синтетически валидны</x:v>
+      </x:c>
+      <x:c r="F54" s="12" t="str">
+        <x:v>valueMissing email; /register</x:v>
+      </x:c>
+      <x:c r="G54" s="12" t="str">
+        <x:v>UI-004</x:v>
+      </x:c>
+      <x:c r="H54" s="12" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="I54" s="12" t="str">
+        <x:v>target/runs/UiRegression/allure-results/427cf2da-a5e0-47db-bf95-1afd1ee08852-result.json</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" ht="64" customHeight="1">
+      <x:c r="A55" s="12" t="str">
+        <x:v>DP-U-REG-EMPTY-03</x:v>
+      </x:c>
+      <x:c r="B55" s="12" t="str">
+        <x:v>DP-U-REG-EMPTY</x:v>
+      </x:c>
+      <x:c r="C55" s="12" t="str">
+        <x:v>RegistrationUiTest.emptyRegistrationFields</x:v>
+      </x:c>
+      <x:c r="D55" s="12" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E55" s="12" t="str">
+        <x:v>Пароль пуст; логин и email синтетически валидны</x:v>
+      </x:c>
+      <x:c r="F55" s="12" t="str">
+        <x:v>valueMissing password; /register</x:v>
+      </x:c>
+      <x:c r="G55" s="12" t="str">
+        <x:v>UI-004</x:v>
+      </x:c>
+      <x:c r="H55" s="12" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="I55" s="12" t="str">
+        <x:v>target/runs/UiRegression/allure-results/f8ce9588-2c78-4077-b098-57458673813e-result.json</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" ht="64" customHeight="1">
+      <x:c r="A56" s="12" t="str">
+        <x:v>DP-U-REG-EMPTY-04</x:v>
+      </x:c>
+      <x:c r="B56" s="12" t="str">
+        <x:v>DP-U-REG-EMPTY</x:v>
+      </x:c>
+      <x:c r="C56" s="12" t="str">
+        <x:v>RegistrationUiTest.emptyRegistrationFields</x:v>
+      </x:c>
+      <x:c r="D56" s="12" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E56" s="12" t="str">
+        <x:v>Все поля пусты</x:v>
+      </x:c>
+      <x:c r="F56" s="12" t="str">
+        <x:v>valueMissing username; /register</x:v>
+      </x:c>
+      <x:c r="G56" s="12" t="str">
+        <x:v>UI-004</x:v>
+      </x:c>
+      <x:c r="H56" s="12" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="I56" s="12" t="str">
+        <x:v>target/runs/UiRegression/allure-results/c5b1c21b-a8ac-4424-8f8a-c180c2a164c6-result.json</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" ht="64" customHeight="1">
+      <x:c r="A57" s="12" t="str">
+        <x:v>DP-U-REG-USERLEN-01</x:v>
+      </x:c>
+      <x:c r="B57" s="12" t="str">
+        <x:v>DP-U-REG-USERLEN</x:v>
+      </x:c>
+      <x:c r="C57" s="12" t="str">
+        <x:v>RegistrationUiTest.usernameBoundaries</x:v>
+      </x:c>
+      <x:c r="D57" s="12" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E57" s="12" t="str">
+        <x:v>Длина логина 2</x:v>
+      </x:c>
+      <x:c r="F57" s="12" t="str">
+        <x:v>Длина поля 2; tooShort=true</x:v>
+      </x:c>
+      <x:c r="G57" s="12" t="str">
+        <x:v>UI-029</x:v>
+      </x:c>
+      <x:c r="H57" s="12" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="I57" s="12" t="str">
+        <x:v>target/runs/UiRegression/allure-results/83e29526-b130-48c1-b5f1-0f9accfd3976-result.json</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" ht="64" customHeight="1">
+      <x:c r="A58" s="12" t="str">
+        <x:v>DP-U-REG-USERLEN-02</x:v>
+      </x:c>
+      <x:c r="B58" s="12" t="str">
+        <x:v>DP-U-REG-USERLEN</x:v>
+      </x:c>
+      <x:c r="C58" s="12" t="str">
+        <x:v>RegistrationUiTest.usernameBoundaries</x:v>
+      </x:c>
+      <x:c r="D58" s="12" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E58" s="12" t="str">
+        <x:v>Длина логина 3</x:v>
+      </x:c>
+      <x:c r="F58" s="12" t="str">
+        <x:v>Длина поля 3; tooShort=false</x:v>
+      </x:c>
+      <x:c r="G58" s="12" t="str">
+        <x:v>UI-029</x:v>
+      </x:c>
+      <x:c r="H58" s="12" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="I58" s="12" t="str">
+        <x:v>target/runs/UiRegression/allure-results/ca928e9a-7b6c-4efe-b582-ec57889046b6-result.json</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" ht="64" customHeight="1">
+      <x:c r="A59" s="12" t="str">
+        <x:v>DP-U-REG-USERLEN-03</x:v>
+      </x:c>
+      <x:c r="B59" s="12" t="str">
+        <x:v>DP-U-REG-USERLEN</x:v>
+      </x:c>
+      <x:c r="C59" s="12" t="str">
+        <x:v>RegistrationUiTest.usernameBoundaries</x:v>
+      </x:c>
+      <x:c r="D59" s="12" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E59" s="12" t="str">
+        <x:v>Длина логина 30</x:v>
+      </x:c>
+      <x:c r="F59" s="12" t="str">
+        <x:v>Длина поля 30; tooShort=false</x:v>
+      </x:c>
+      <x:c r="G59" s="12" t="str">
+        <x:v>UI-029</x:v>
+      </x:c>
+      <x:c r="H59" s="12" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="I59" s="12" t="str">
+        <x:v>target/runs/UiRegression/allure-results/09b4c724-791f-4509-99dc-eb41217598e3-result.json</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" ht="64" customHeight="1">
+      <x:c r="A60" s="12" t="str">
+        <x:v>DP-U-REG-USERLEN-04</x:v>
+      </x:c>
+      <x:c r="B60" s="12" t="str">
+        <x:v>DP-U-REG-USERLEN</x:v>
+      </x:c>
+      <x:c r="C60" s="12" t="str">
+        <x:v>RegistrationUiTest.usernameBoundaries</x:v>
+      </x:c>
+      <x:c r="D60" s="12" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E60" s="12" t="str">
+        <x:v>Длина логина 31</x:v>
+      </x:c>
+      <x:c r="F60" s="12" t="str">
+        <x:v>Длина поля 30; tooShort=false</x:v>
+      </x:c>
+      <x:c r="G60" s="12" t="str">
+        <x:v>UI-029</x:v>
+      </x:c>
+      <x:c r="H60" s="12" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="I60" s="12" t="str">
+        <x:v>target/runs/UiRegression/allure-results/55f17541-1327-471c-8901-d1ba91d1c68e-result.json</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" ht="64" customHeight="1">
+      <x:c r="A61" s="12" t="str">
+        <x:v>DP-U-REG-PASSLEN-01</x:v>
+      </x:c>
+      <x:c r="B61" s="12" t="str">
+        <x:v>DP-U-REG-PASSLEN</x:v>
+      </x:c>
+      <x:c r="C61" s="12" t="str">
+        <x:v>RegistrationUiTest.passwordBoundaries</x:v>
+      </x:c>
+      <x:c r="D61" s="12" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E61" s="12" t="str">
+        <x:v>Длина синтетического пароля 7</x:v>
+      </x:c>
+      <x:c r="F61" s="12" t="str">
+        <x:v>Длина поля 7; tooShort=true</x:v>
+      </x:c>
+      <x:c r="G61" s="12" t="str">
+        <x:v>UI-030</x:v>
+      </x:c>
+      <x:c r="H61" s="12" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="I61" s="12" t="str">
+        <x:v>target/runs/UiRegression/allure-results/eb35ca40-ef65-4ac6-a451-0df726271023-result.json</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62" ht="64" customHeight="1">
+      <x:c r="A62" s="12" t="str">
+        <x:v>DP-U-REG-PASSLEN-02</x:v>
+      </x:c>
+      <x:c r="B62" s="12" t="str">
+        <x:v>DP-U-REG-PASSLEN</x:v>
+      </x:c>
+      <x:c r="C62" s="12" t="str">
+        <x:v>RegistrationUiTest.passwordBoundaries</x:v>
+      </x:c>
+      <x:c r="D62" s="12" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E62" s="12" t="str">
+        <x:v>Длина синтетического пароля 8</x:v>
+      </x:c>
+      <x:c r="F62" s="12" t="str">
+        <x:v>Длина поля 8; tooShort=false</x:v>
+      </x:c>
+      <x:c r="G62" s="12" t="str">
+        <x:v>UI-030</x:v>
+      </x:c>
+      <x:c r="H62" s="12" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="I62" s="12" t="str">
+        <x:v>target/runs/UiRegression/allure-results/b845f2e1-ad33-4b47-8bdd-93a859a83929-result.json</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63" ht="64" customHeight="1">
+      <x:c r="A63" s="12" t="str">
+        <x:v>DP-U-REG-PASSLEN-03</x:v>
+      </x:c>
+      <x:c r="B63" s="12" t="str">
+        <x:v>DP-U-REG-PASSLEN</x:v>
+      </x:c>
+      <x:c r="C63" s="12" t="str">
+        <x:v>RegistrationUiTest.passwordBoundaries</x:v>
+      </x:c>
+      <x:c r="D63" s="12" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E63" s="12" t="str">
+        <x:v>Длина синтетического пароля 72</x:v>
+      </x:c>
+      <x:c r="F63" s="12" t="str">
+        <x:v>Длина поля 72; tooShort=false</x:v>
+      </x:c>
+      <x:c r="G63" s="12" t="str">
+        <x:v>UI-030</x:v>
+      </x:c>
+      <x:c r="H63" s="12" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="I63" s="12" t="str">
+        <x:v>target/runs/UiRegression/allure-results/cdb7e61e-d542-490d-8be5-cc471ae1a47a-result.json</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64" ht="64" customHeight="1">
+      <x:c r="A64" s="12" t="str">
+        <x:v>DP-U-REG-PASSLEN-04</x:v>
+      </x:c>
+      <x:c r="B64" s="12" t="str">
+        <x:v>DP-U-REG-PASSLEN</x:v>
+      </x:c>
+      <x:c r="C64" s="12" t="str">
+        <x:v>RegistrationUiTest.passwordBoundaries</x:v>
+      </x:c>
+      <x:c r="D64" s="12" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E64" s="12" t="str">
+        <x:v>Длина синтетического пароля 73</x:v>
+      </x:c>
+      <x:c r="F64" s="12" t="str">
+        <x:v>Длина поля 72; tooShort=false</x:v>
+      </x:c>
+      <x:c r="G64" s="12" t="str">
+        <x:v>UI-030</x:v>
+      </x:c>
+      <x:c r="H64" s="12" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="I64" s="12" t="str">
+        <x:v>target/runs/UiRegression/allure-results/269bb215-e01f-40f3-8307-03ed12f7b717-result.json</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65" ht="64" customHeight="1">
+      <x:c r="A65" s="12" t="str">
+        <x:v>DP-U-REG-EMAIL-01</x:v>
+      </x:c>
+      <x:c r="B65" s="12" t="str">
+        <x:v>DP-U-REG-EMAIL</x:v>
+      </x:c>
+      <x:c r="C65" s="12" t="str">
+        <x:v>RegistrationUiTest.invalidEmails</x:v>
+      </x:c>
+      <x:c r="D65" s="12" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E65" s="12" t="str">
+        <x:v>plainaddress</x:v>
+      </x:c>
+      <x:c r="F65" s="12" t="str">
+        <x:v>typeMismatch=true</x:v>
+      </x:c>
+      <x:c r="G65" s="12" t="str">
+        <x:v>UI-003</x:v>
+      </x:c>
+      <x:c r="H65" s="12" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="I65" s="12" t="str">
+        <x:v>target/runs/UiRegression/allure-results/dae21a8b-febc-45ec-b3af-410f5ca3c364-result.json</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66" ht="64" customHeight="1">
+      <x:c r="A66" s="12" t="str">
+        <x:v>DP-U-REG-EMAIL-02</x:v>
+      </x:c>
+      <x:c r="B66" s="12" t="str">
+        <x:v>DP-U-REG-EMAIL</x:v>
+      </x:c>
+      <x:c r="C66" s="12" t="str">
+        <x:v>RegistrationUiTest.invalidEmails</x:v>
+      </x:c>
+      <x:c r="D66" s="12" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E66" s="12" t="str">
+        <x:v>user@</x:v>
+      </x:c>
+      <x:c r="F66" s="12" t="str">
+        <x:v>typeMismatch=true</x:v>
+      </x:c>
+      <x:c r="G66" s="12" t="str">
+        <x:v>UI-003</x:v>
+      </x:c>
+      <x:c r="H66" s="12" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="I66" s="12" t="str">
+        <x:v>target/runs/UiRegression/allure-results/5b247895-840b-4b56-b977-a15687b7ec02-result.json</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67" ht="64" customHeight="1">
+      <x:c r="A67" s="12" t="str">
+        <x:v>DP-U-REG-EMAIL-03</x:v>
+      </x:c>
+      <x:c r="B67" s="12" t="str">
+        <x:v>DP-U-REG-EMAIL</x:v>
+      </x:c>
+      <x:c r="C67" s="12" t="str">
+        <x:v>RegistrationUiTest.invalidEmails</x:v>
+      </x:c>
+      <x:c r="D67" s="12" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E67" s="12" t="str">
+        <x:v>@example.com</x:v>
+      </x:c>
+      <x:c r="F67" s="12" t="str">
+        <x:v>typeMismatch=true</x:v>
+      </x:c>
+      <x:c r="G67" s="12" t="str">
+        <x:v>UI-003</x:v>
+      </x:c>
+      <x:c r="H67" s="12" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="I67" s="12" t="str">
+        <x:v>target/runs/UiRegression/allure-results/f3acad7c-96ca-42c2-8e85-9ec752e7c026-result.json</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68" ht="64" customHeight="1">
+      <x:c r="A68" s="12" t="str">
+        <x:v>DP-U-REG-EMAIL-04</x:v>
+      </x:c>
+      <x:c r="B68" s="12" t="str">
+        <x:v>DP-U-REG-EMAIL</x:v>
+      </x:c>
+      <x:c r="C68" s="12" t="str">
+        <x:v>RegistrationUiTest.invalidEmails</x:v>
+      </x:c>
+      <x:c r="D68" s="12" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E68" s="12" t="str">
+        <x:v>user name@example.com</x:v>
+      </x:c>
+      <x:c r="F68" s="12" t="str">
+        <x:v>typeMismatch=true</x:v>
+      </x:c>
+      <x:c r="G68" s="12" t="str">
+        <x:v>UI-003</x:v>
+      </x:c>
+      <x:c r="H68" s="12" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="I68" s="12" t="str">
+        <x:v>target/runs/UiRegression/allure-results/32c60b63-03b9-4955-8604-6df361aa5ef2-result.json</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69" ht="64" customHeight="1">
+      <x:c r="A69" s="12" t="str">
+        <x:v>DP-U-REG-DUP-01</x:v>
+      </x:c>
+      <x:c r="B69" s="12" t="str">
+        <x:v>DP-U-REG-DUP</x:v>
+      </x:c>
+      <x:c r="C69" s="12" t="str">
+        <x:v>RegistrationUiTest.duplicateRegistrationData</x:v>
+      </x:c>
+      <x:c r="D69" s="12" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E69" s="12" t="str">
+        <x:v>Занят логин; новый email</x:v>
+      </x:c>
+      <x:c r="F69" s="12" t="str">
+        <x:v>«Логин уже занят»; БД без новых пользователей</x:v>
+      </x:c>
+      <x:c r="G69" s="12" t="str">
+        <x:v>UI-002</x:v>
+      </x:c>
+      <x:c r="H69" s="12" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="I69" s="12" t="str">
+        <x:v>target/runs/UiRegression/allure-results/8f8e5b62-c315-4cc0-97a1-260723c798e5-result.json</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70" ht="64" customHeight="1">
+      <x:c r="A70" s="12" t="str">
+        <x:v>DP-U-REG-DUP-02</x:v>
+      </x:c>
+      <x:c r="B70" s="12" t="str">
+        <x:v>DP-U-REG-DUP</x:v>
+      </x:c>
+      <x:c r="C70" s="12" t="str">
+        <x:v>RegistrationUiTest.duplicateRegistrationData</x:v>
+      </x:c>
+      <x:c r="D70" s="12" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E70" s="12" t="str">
+        <x:v>Новый логин; занят email</x:v>
+      </x:c>
+      <x:c r="F70" s="12" t="str">
+        <x:v>«Email уже зарегистрирован»; БД без новых пользователей</x:v>
+      </x:c>
+      <x:c r="G70" s="12" t="str">
+        <x:v>UI-021</x:v>
+      </x:c>
+      <x:c r="H70" s="12" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="I70" s="12" t="str">
+        <x:v>target/runs/UiRegression/allure-results/466308d2-e763-41f3-abee-b5b6da5f718e-result.json</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71" ht="64" customHeight="1">
+      <x:c r="A71" s="12" t="str">
+        <x:v>DP-U-REG-DUP-03</x:v>
+      </x:c>
+      <x:c r="B71" s="12" t="str">
+        <x:v>DP-U-REG-DUP</x:v>
+      </x:c>
+      <x:c r="C71" s="12" t="str">
+        <x:v>RegistrationUiTest.duplicateRegistrationData</x:v>
+      </x:c>
+      <x:c r="D71" s="12" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E71" s="12" t="str">
+        <x:v>Заняты логин и email</x:v>
+      </x:c>
+      <x:c r="F71" s="12" t="str">
+        <x:v>«Логин уже занят»; БД без новых пользователей</x:v>
+      </x:c>
+      <x:c r="G71" s="12" t="str">
+        <x:v>UI-040</x:v>
+      </x:c>
+      <x:c r="H71" s="12" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="I71" s="12" t="str">
+        <x:v>target/runs/UiRegression/allure-results/c094df9f-31bb-4b55-92f0-49ca7ec918fd-result.json</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72" ht="64" customHeight="1">
+      <x:c r="A72" s="12" t="str">
+        <x:v>DP-U-TASK-FIELDS-01</x:v>
+      </x:c>
+      <x:c r="B72" s="12" t="str">
+        <x:v>DP-U-TASK-FIELDS</x:v>
+      </x:c>
+      <x:c r="C72" s="12" t="str">
+        <x:v>TaskUiTest.taskData</x:v>
+      </x:c>
+      <x:c r="D72" s="12" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E72" s="12" t="str">
+        <x:v>TODO; LOW; 2026-12-01</x:v>
+      </x:c>
+      <x:c r="F72" s="12" t="str">
+        <x:v>Поля задачи в БД совпадают с вводом</x:v>
+      </x:c>
+      <x:c r="G72" s="12" t="str">
+        <x:v>UI-035</x:v>
+      </x:c>
+      <x:c r="H72" s="12" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="I72" s="12" t="str">
+        <x:v>target/runs/UiRegression/allure-results/2bea8319-becc-4fc9-8fcc-374f5bd672ae-result.json</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73" ht="64" customHeight="1">
+      <x:c r="A73" s="12" t="str">
+        <x:v>DP-U-TASK-FIELDS-02</x:v>
+      </x:c>
+      <x:c r="B73" s="12" t="str">
+        <x:v>DP-U-TASK-FIELDS</x:v>
+      </x:c>
+      <x:c r="C73" s="12" t="str">
+        <x:v>TaskUiTest.taskData</x:v>
+      </x:c>
+      <x:c r="D73" s="12" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E73" s="12" t="str">
+        <x:v>IN_PROGRESS; MEDIUM; 2026-12-15</x:v>
+      </x:c>
+      <x:c r="F73" s="12" t="str">
+        <x:v>Поля задачи в БД совпадают с вводом</x:v>
+      </x:c>
+      <x:c r="G73" s="12" t="str">
+        <x:v>UI-035</x:v>
+      </x:c>
+      <x:c r="H73" s="12" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="I73" s="12" t="str">
+        <x:v>target/runs/UiRegression/allure-results/f059d4a6-b202-4989-99ff-0749961e1618-result.json</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74" ht="64" customHeight="1">
+      <x:c r="A74" s="12" t="str">
+        <x:v>DP-U-TASK-FIELDS-03</x:v>
+      </x:c>
+      <x:c r="B74" s="12" t="str">
+        <x:v>DP-U-TASK-FIELDS</x:v>
+      </x:c>
+      <x:c r="C74" s="12" t="str">
+        <x:v>TaskUiTest.taskData</x:v>
+      </x:c>
+      <x:c r="D74" s="12" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E74" s="12" t="str">
+        <x:v>DONE; HIGH; 2026-12-31</x:v>
+      </x:c>
+      <x:c r="F74" s="12" t="str">
+        <x:v>Поля задачи в БД совпадают с вводом</x:v>
+      </x:c>
+      <x:c r="G74" s="12" t="str">
+        <x:v>UI-035</x:v>
+      </x:c>
+      <x:c r="H74" s="12" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="I74" s="12" t="str">
+        <x:v>target/runs/UiRegression/allure-results/42a225c1-3b79-46d7-8c32-649fb23388ee-result.json</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75" ht="64" customHeight="1">
+      <x:c r="A75" s="12" t="str">
+        <x:v>DP-U-TASK-BADTITLE-01</x:v>
+      </x:c>
+      <x:c r="B75" s="12" t="str">
+        <x:v>DP-U-TASK-BADTITLE</x:v>
+      </x:c>
+      <x:c r="C75" s="12" t="str">
+        <x:v>TaskUiTest.invalidTaskTitles</x:v>
+      </x:c>
+      <x:c r="D75" s="12" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E75" s="12" t="str">
+        <x:v>Название длиной 1</x:v>
+      </x:c>
+      <x:c r="F75" s="12" t="str">
+        <x:v>/tasks/new; ошибка длины 3–100</x:v>
+      </x:c>
+      <x:c r="G75" s="12" t="str">
+        <x:v>UI-036</x:v>
+      </x:c>
+      <x:c r="H75" s="12" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="I75" s="12" t="str">
+        <x:v>target/runs/UiRegression/allure-results/61f4325b-1515-452e-b882-39352ded11ad-result.json</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="76" ht="64" customHeight="1">
+      <x:c r="A76" s="12" t="str">
+        <x:v>DP-U-TASK-BADTITLE-02</x:v>
+      </x:c>
+      <x:c r="B76" s="12" t="str">
+        <x:v>DP-U-TASK-BADTITLE</x:v>
+      </x:c>
+      <x:c r="C76" s="12" t="str">
+        <x:v>TaskUiTest.invalidTaskTitles</x:v>
+      </x:c>
+      <x:c r="D76" s="12" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E76" s="12" t="str">
+        <x:v>Название длиной 2</x:v>
+      </x:c>
+      <x:c r="F76" s="12" t="str">
+        <x:v>/tasks/new; ошибка длины 3–100</x:v>
+      </x:c>
+      <x:c r="G76" s="12" t="str">
+        <x:v>UI-036</x:v>
+      </x:c>
+      <x:c r="H76" s="12" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="I76" s="12" t="str">
+        <x:v>target/runs/UiRegression/allure-results/196dec66-cb6f-4ffe-95bb-5d73f29f1d46-result.json</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="77" ht="64" customHeight="1">
+      <x:c r="A77" s="12" t="str">
+        <x:v>DP-U-TASK-TITLELEN-01</x:v>
+      </x:c>
+      <x:c r="B77" s="12" t="str">
+        <x:v>DP-U-TASK-TITLELEN</x:v>
+      </x:c>
+      <x:c r="C77" s="12" t="str">
+        <x:v>TaskUiTest.validTaskTitleLengths</x:v>
+      </x:c>
+      <x:c r="D77" s="12" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E77" s="12" t="str">
+        <x:v>Название длиной 3; description=AUTOTEST_&lt;uuid&gt;; прочие поля не меняются</x:v>
+      </x:c>
+      <x:c r="F77" s="12" t="str">
+        <x:v>Непустой ID задачи найден в БД</x:v>
+      </x:c>
+      <x:c r="G77" s="12" t="str">
+        <x:v>UI-037</x:v>
+      </x:c>
+      <x:c r="H77" s="12" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="I77" s="12" t="str">
+        <x:v>target/runs/UiRegression/allure-results/7cc33ab2-cffa-41a8-9d56-d0777bd1d77f-result.json</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="78" ht="64" customHeight="1">
+      <x:c r="A78" s="12" t="str">
+        <x:v>DP-U-TASK-TITLELEN-02</x:v>
+      </x:c>
+      <x:c r="B78" s="12" t="str">
+        <x:v>DP-U-TASK-TITLELEN</x:v>
+      </x:c>
+      <x:c r="C78" s="12" t="str">
+        <x:v>TaskUiTest.validTaskTitleLengths</x:v>
+      </x:c>
+      <x:c r="D78" s="12" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E78" s="12" t="str">
+        <x:v>Название длиной 4; description=AUTOTEST_&lt;uuid&gt;; прочие поля не меняются</x:v>
+      </x:c>
+      <x:c r="F78" s="12" t="str">
+        <x:v>Непустой ID задачи найден в БД</x:v>
+      </x:c>
+      <x:c r="G78" s="12" t="str">
+        <x:v>UI-037</x:v>
+      </x:c>
+      <x:c r="H78" s="12" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="I78" s="12" t="str">
+        <x:v>target/runs/UiRegression/allure-results/c5ecc4d5-4531-4547-8a48-cb4df28de748-result.json</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="79" ht="64" customHeight="1">
+      <x:c r="A79" s="12" t="str">
+        <x:v>DP-U-TASK-TITLELEN-03</x:v>
+      </x:c>
+      <x:c r="B79" s="12" t="str">
+        <x:v>DP-U-TASK-TITLELEN</x:v>
+      </x:c>
+      <x:c r="C79" s="12" t="str">
+        <x:v>TaskUiTest.validTaskTitleLengths</x:v>
+      </x:c>
+      <x:c r="D79" s="12" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E79" s="12" t="str">
+        <x:v>Название длиной 99; description=AUTOTEST_&lt;uuid&gt;; прочие поля не меняются</x:v>
+      </x:c>
+      <x:c r="F79" s="12" t="str">
+        <x:v>Непустой ID задачи найден в БД</x:v>
+      </x:c>
+      <x:c r="G79" s="12" t="str">
+        <x:v>UI-037</x:v>
+      </x:c>
+      <x:c r="H79" s="12" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="I79" s="12" t="str">
+        <x:v>target/runs/UiRegression/allure-results/8b526e98-c296-40ab-982e-bbd6a37aee3d-result.json</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="80" ht="64" customHeight="1">
+      <x:c r="A80" s="12" t="str">
+        <x:v>DP-U-TASK-TITLELEN-04</x:v>
+      </x:c>
+      <x:c r="B80" s="12" t="str">
+        <x:v>DP-U-TASK-TITLELEN</x:v>
+      </x:c>
+      <x:c r="C80" s="12" t="str">
+        <x:v>TaskUiTest.validTaskTitleLengths</x:v>
+      </x:c>
+      <x:c r="D80" s="12" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E80" s="12" t="str">
+        <x:v>Название длиной 100; description=AUTOTEST_&lt;uuid&gt;; прочие поля не меняются</x:v>
+      </x:c>
+      <x:c r="F80" s="12" t="str">
+        <x:v>Непустой ID задачи найден в БД</x:v>
+      </x:c>
+      <x:c r="G80" s="12" t="str">
+        <x:v>UI-037</x:v>
+      </x:c>
+      <x:c r="H80" s="12" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="I80" s="12" t="str">
+        <x:v>target/runs/UiRegression/allure-results/37657d9c-c850-4fb7-a812-5d5e00e68f3a-result.json</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="81" ht="64" customHeight="1">
+      <x:c r="A81" s="12" t="str">
+        <x:v>DP-U-TASK-DESCLEN-01</x:v>
+      </x:c>
+      <x:c r="B81" s="12" t="str">
+        <x:v>DP-U-TASK-DESCLEN</x:v>
+      </x:c>
+      <x:c r="C81" s="12" t="str">
+        <x:v>TaskUiTest.taskDescriptionLengths</x:v>
+      </x:c>
+      <x:c r="D81" s="12" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E81" s="12" t="str">
+        <x:v>Описание длиной 0</x:v>
+      </x:c>
+      <x:c r="F81" s="12" t="str">
+        <x:v>Длина поля 0; это описание сохранено в БД</x:v>
+      </x:c>
+      <x:c r="G81" s="12" t="str">
+        <x:v>UI-038</x:v>
+      </x:c>
+      <x:c r="H81" s="12" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="I81" s="12" t="str">
+        <x:v>target/runs/UiRegression/allure-results/9fd88c60-eceb-427c-90d2-4719294537a8-result.json</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="82" ht="64" customHeight="1">
+      <x:c r="A82" s="12" t="str">
+        <x:v>DP-U-TASK-DESCLEN-02</x:v>
+      </x:c>
+      <x:c r="B82" s="12" t="str">
+        <x:v>DP-U-TASK-DESCLEN</x:v>
+      </x:c>
+      <x:c r="C82" s="12" t="str">
+        <x:v>TaskUiTest.taskDescriptionLengths</x:v>
+      </x:c>
+      <x:c r="D82" s="12" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E82" s="12" t="str">
+        <x:v>Описание длиной 1</x:v>
+      </x:c>
+      <x:c r="F82" s="12" t="str">
+        <x:v>Длина поля 1; это описание сохранено в БД</x:v>
+      </x:c>
+      <x:c r="G82" s="12" t="str">
+        <x:v>UI-038</x:v>
+      </x:c>
+      <x:c r="H82" s="12" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="I82" s="12" t="str">
+        <x:v>target/runs/UiRegression/allure-results/04e8a90c-02b0-4d1b-b352-a982ea222f52-result.json</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="83" ht="64" customHeight="1">
+      <x:c r="A83" s="12" t="str">
+        <x:v>DP-U-TASK-DESCLEN-03</x:v>
+      </x:c>
+      <x:c r="B83" s="12" t="str">
+        <x:v>DP-U-TASK-DESCLEN</x:v>
+      </x:c>
+      <x:c r="C83" s="12" t="str">
+        <x:v>TaskUiTest.taskDescriptionLengths</x:v>
+      </x:c>
+      <x:c r="D83" s="12" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E83" s="12" t="str">
+        <x:v>Описание длиной 999</x:v>
+      </x:c>
+      <x:c r="F83" s="12" t="str">
+        <x:v>Длина поля 999; это описание сохранено в БД</x:v>
+      </x:c>
+      <x:c r="G83" s="12" t="str">
+        <x:v>UI-038</x:v>
+      </x:c>
+      <x:c r="H83" s="12" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="I83" s="12" t="str">
+        <x:v>target/runs/UiRegression/allure-results/658bfdb8-3388-4b80-9552-361c07b2d029-result.json</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="84" ht="64" customHeight="1">
+      <x:c r="A84" s="12" t="str">
+        <x:v>DP-U-TASK-DESCLEN-04</x:v>
+      </x:c>
+      <x:c r="B84" s="12" t="str">
+        <x:v>DP-U-TASK-DESCLEN</x:v>
+      </x:c>
+      <x:c r="C84" s="12" t="str">
+        <x:v>TaskUiTest.taskDescriptionLengths</x:v>
+      </x:c>
+      <x:c r="D84" s="12" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E84" s="12" t="str">
+        <x:v>Описание длиной 1000</x:v>
+      </x:c>
+      <x:c r="F84" s="12" t="str">
+        <x:v>Длина поля 1000; это описание сохранено в БД</x:v>
+      </x:c>
+      <x:c r="G84" s="12" t="str">
+        <x:v>UI-038</x:v>
+      </x:c>
+      <x:c r="H84" s="12" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="I84" s="12" t="str">
+        <x:v>target/runs/UiRegression/allure-results/4b6caea7-4394-4bc6-8b55-9a18248029d8-result.json</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="85" ht="64" customHeight="1">
+      <x:c r="A85" s="12" t="str">
+        <x:v>DP-U-TASK-DESCLEN-05</x:v>
+      </x:c>
+      <x:c r="B85" s="12" t="str">
+        <x:v>DP-U-TASK-DESCLEN</x:v>
+      </x:c>
+      <x:c r="C85" s="12" t="str">
+        <x:v>TaskUiTest.taskDescriptionLengths</x:v>
+      </x:c>
+      <x:c r="D85" s="12" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E85" s="12" t="str">
+        <x:v>Описание длиной 1001</x:v>
+      </x:c>
+      <x:c r="F85" s="12" t="str">
+        <x:v>Длина поля 1000; это описание сохранено в БД</x:v>
+      </x:c>
+      <x:c r="G85" s="12" t="str">
+        <x:v>UI-038</x:v>
+      </x:c>
+      <x:c r="H85" s="12" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="I85" s="12" t="str">
+        <x:v>target/runs/UiRegression/allure-results/f30d4755-b563-45b9-8d46-d144f57116f0-result.json</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R18a4006da9944308"/>
+  </x:tableParts>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="43" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="70" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="80" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="58" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="64" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="15" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="38" customHeight="1">
+      <x:c r="A1" s="13" t="str">
+        <x:v>ID</x:v>
+      </x:c>
+      <x:c r="B1" s="13" t="str">
+        <x:v>Категория</x:v>
+      </x:c>
+      <x:c r="C1" s="13" t="str">
+        <x:v>Назначение</x:v>
+      </x:c>
+      <x:c r="D1" s="13" t="str">
+        <x:v>Пример</x:v>
+      </x:c>
+      <x:c r="E1" s="13" t="str">
+        <x:v>Правила подготовки / безопасности</x:v>
+      </x:c>
+      <x:c r="F1" s="13" t="str">
+        <x:v>Источник / DataProvider</x:v>
+      </x:c>
+      <x:c r="G1" s="13" t="str">
+        <x:v>Актуальные кейсы</x:v>
+      </x:c>
+      <x:c r="H1" s="13" t="str">
+        <x:v>Вариантов</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="78" customHeight="1">
+      <x:c r="A2" s="12" t="str">
+        <x:v>TD-NO-CSRF</x:v>
+      </x:c>
+      <x:c r="B2" s="12" t="str">
+        <x:v>CSRF</x:v>
+      </x:c>
+      <x:c r="C2" s="12" t="str">
+        <x:v>Запрос изменения данных без CSRF</x:v>
+      </x:c>
+      <x:c r="D2" s="12" t="str">
+        <x:v>X-CSRF-TOKEN отсутствует</x:v>
+      </x:c>
+      <x:c r="E2" s="12" t="str">
+        <x:v>Использовать авторизованную сессию; намеренно не отправлять токен; проверить HTTP 403 и отсутствие изменений</x:v>
+      </x:c>
+      <x:c r="F2" s="12" t="str">
+        <x:v>Исторический план</x:v>
+      </x:c>
+      <x:c r="G2" s="12" t="str">
+        <x:v>Не используется актуальными кейсами</x:v>
+      </x:c>
+      <x:c r="H2" s="12"/>
+    </x:row>
+    <x:row r="3" ht="78" customHeight="1">
+      <x:c r="A3" s="12" t="str">
+        <x:v>TD-HTML-TEXT</x:v>
+      </x:c>
+      <x:c r="B3" s="12" t="str">
+        <x:v>Текст</x:v>
+      </x:c>
+      <x:c r="C3" s="12" t="str">
+        <x:v>HTML-подобное значение</x:v>
+      </x:c>
+      <x:c r="D3" s="12" t="str">
+        <x:v>&lt;script&gt;alert(1)&lt;/script&gt;</x:v>
+      </x:c>
+      <x:c r="E3" s="12" t="str">
+        <x:v>Проверять отображение как текста, без выполнения</x:v>
+      </x:c>
+      <x:c r="F3" s="12" t="str">
+        <x:v>Исторический план</x:v>
+      </x:c>
+      <x:c r="G3" s="12" t="str">
+        <x:v>Не используется актуальными кейсами</x:v>
+      </x:c>
+      <x:c r="H3" s="12"/>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2714dcea9ad04848"/>
   </x:tableParts>
 </x:worksheet>
 </file>